--- a/Muestreo de datos sin la barberia.xlsx
+++ b/Muestreo de datos sin la barberia.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\leand\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\leand\Desktop\DOO\DOO\Barberia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9AB6BC2-F456-4BE6-A774-E9D7C346C668}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85761C5D-CB5A-4CF0-867F-D92DC73BE9A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="7" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="3" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Modelo de Dominio" sheetId="1" r:id="rId1"/>
@@ -363,7 +363,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1708" uniqueCount="333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1690" uniqueCount="333">
   <si>
     <t>Ir a objetos de dominio &gt;&gt;&gt;&gt;</t>
   </si>
@@ -614,18 +614,9 @@
     <t>Numérico (Entero)</t>
   </si>
   <si>
-    <t>Debe corresponder a un número celular colombiano de 10 dígitos que inicie en 3.</t>
-  </si>
-  <si>
-    <t>Debe tener formato de correo electrónico válido (usuario@dominio). Se debe asegurar una sanitización del dato, para garantizar que dentro de su contenido no tenga cualquier tipo de intento de ataque o instrucción maliciosa.</t>
-  </si>
-  <si>
     <t>Lógico</t>
   </si>
   <si>
-    <t>Se calcula evaluando si el barbero tiene al menos una Agenda vigente; si no tiene ninguna, no es vigente.</t>
-  </si>
-  <si>
     <t>Representa el primer nombre del barbero que trabaja en barbería. Su tipo de dato es texto, su valor por defecto es el vacio y no es permitido</t>
   </si>
   <si>
@@ -897,15 +888,6 @@
   </si>
   <si>
     <t>Representa la hora a la que cierra la barbería. Su valor por defecto es 00:00 y no es permitido</t>
-  </si>
-  <si>
-    <t>Representa la fecha en el que el dueño creo el horario para la barberia. Es dato calculado que el sistema toma la fecha de hoy cuando el dueño crea el horario</t>
-  </si>
-  <si>
-    <t>Representa la fecha en el que el dueño decidio que este horario ya no va a ser disponible. Es un dato calculado que el sistema toma la fecha de hoy, cuando el dueño cambia el estado de vigencia</t>
-  </si>
-  <si>
-    <t>Representa si este horario lo sigue o no usando la barberia. Una vez que el dueño cambie este estado a no vigente, no se puede volver a cambiar</t>
   </si>
   <si>
     <t>Combinacion única que indica que no puede existir más de un horario con la misma barberia, dia de la semana, hora de apertura y cierre</t>
@@ -1364,6 +1346,24 @@
   </si>
   <si>
     <t>horario del barbero</t>
+  </si>
+  <si>
+    <t>Debe de tener un @, tener un dominio de correo después del @, debe de terminar en el dominio web del correo, como .com, .co y no debe de tener espacios en blanco</t>
+  </si>
+  <si>
+    <t>+0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deben de ser solo números que cumplan un número de teléfono válido </t>
+  </si>
+  <si>
+    <t>0000</t>
+  </si>
+  <si>
+    <t>Se calcula evaluando si el barbero tiene al menos un HorarioBarbero vigente; si no tiene ninguna, no es vigente.</t>
+  </si>
+  <si>
+    <t>Entero</t>
   </si>
 </sst>
 </file>
@@ -1624,7 +1624,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -1728,12 +1728,25 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="136">
+  <cellXfs count="138">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1778,12 +1791,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -1864,9 +1871,6 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2100,6 +2104,19 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -2192,41 +2209,59 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>182879</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>608760</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>32400</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>556260</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>70532</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Imagen 2">
+        <xdr:cNvPr id="3" name="Imagen 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{40936285-831E-D4B6-B75F-313BA6A37125}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvPicPr/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
       </xdr:blipFill>
-      <xdr:spPr>
+      <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="0" y="190440"/>
-          <a:ext cx="10830240" cy="6890400"/>
+          <a:off x="0" y="182879"/>
+          <a:ext cx="7345680" cy="5191173"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -4241,271 +4276,271 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="27" t="s">
+      <c r="B1" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
-      <c r="I1" s="26"/>
-      <c r="J1" s="26"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
+      <c r="J1" s="24"/>
     </row>
     <row r="2" spans="1:10" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="45" t="s">
+      <c r="A2" s="43" t="s">
         <v>66</v>
       </c>
-      <c r="B2" s="45" t="s">
+      <c r="B2" s="43" t="s">
+        <v>134</v>
+      </c>
+      <c r="C2" s="43" t="s">
+        <v>135</v>
+      </c>
+      <c r="D2" s="43" t="s">
+        <v>136</v>
+      </c>
+      <c r="E2" s="43" t="s">
         <v>137</v>
       </c>
-      <c r="C2" s="45" t="s">
+      <c r="F2" s="43" t="s">
         <v>138</v>
       </c>
-      <c r="D2" s="45" t="s">
+      <c r="G2" s="44" t="s">
         <v>139</v>
       </c>
-      <c r="E2" s="45" t="s">
+      <c r="H2" s="44" t="s">
         <v>140</v>
       </c>
-      <c r="F2" s="45" t="s">
+      <c r="I2" s="44" t="s">
         <v>141</v>
       </c>
-      <c r="G2" s="46" t="s">
+      <c r="J2" s="45" t="s">
         <v>142</v>
       </c>
-      <c r="H2" s="46" t="s">
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="B3" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="C3" s="22" t="s">
+        <v>95</v>
+      </c>
+      <c r="D3" s="22" t="s">
+        <v>96</v>
+      </c>
+      <c r="E3" s="22" t="s">
+        <v>97</v>
+      </c>
+      <c r="F3" s="22" t="s">
         <v>143</v>
       </c>
-      <c r="I2" s="46" t="s">
+      <c r="G3" s="22" t="s">
+        <v>99</v>
+      </c>
+      <c r="H3" s="36" t="s">
         <v>144</v>
       </c>
-      <c r="J2" s="47" t="s">
+      <c r="I3" s="36" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A3" s="23" t="s">
-        <v>70</v>
-      </c>
-      <c r="B3" s="24" t="s">
-        <v>97</v>
-      </c>
-      <c r="C3" s="24" t="s">
-        <v>98</v>
-      </c>
-      <c r="D3" s="24" t="s">
-        <v>99</v>
-      </c>
-      <c r="E3" s="24" t="s">
-        <v>100</v>
-      </c>
-      <c r="F3" s="24" t="s">
+      <c r="J3" s="37" t="s">
         <v>146</v>
       </c>
-      <c r="G3" s="24" t="s">
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" s="24">
+        <v>1</v>
+      </c>
+      <c r="B4" s="24" t="s">
         <v>102</v>
       </c>
-      <c r="H3" s="38" t="s">
+      <c r="C4" s="24"/>
+      <c r="D4" s="24" t="s">
         <v>147</v>
       </c>
-      <c r="I3" s="38" t="s">
-        <v>148</v>
-      </c>
-      <c r="J3" s="39" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A4" s="26">
-        <v>1</v>
-      </c>
-      <c r="B4" s="26" t="s">
-        <v>105</v>
-      </c>
-      <c r="C4" s="26"/>
-      <c r="D4" s="26" t="s">
-        <v>150</v>
-      </c>
-      <c r="E4" s="26"/>
-      <c r="F4" s="40" t="s">
-        <v>109</v>
-      </c>
-      <c r="G4" s="26">
+      <c r="E4" s="24"/>
+      <c r="F4" s="38" t="s">
+        <v>106</v>
+      </c>
+      <c r="G4" s="24">
         <v>3234528921</v>
       </c>
-      <c r="H4" s="26">
+      <c r="H4" s="24">
         <v>0</v>
       </c>
-      <c r="I4" s="26" t="s">
-        <v>127</v>
-      </c>
-      <c r="J4" s="26" t="str">
+      <c r="I4" s="24" t="s">
+        <v>124</v>
+      </c>
+      <c r="J4" s="24" t="str">
         <f>_xlfn.CONCAT(B4,"-",C4,"-",D4,"-",E4,"-",F4,"-",G4)</f>
         <v>Juan--Gómez--+57-3234528921</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A5" s="26">
+      <c r="A5" s="24">
         <v>2</v>
       </c>
-      <c r="B5" s="26" t="s">
-        <v>151</v>
-      </c>
-      <c r="C5" s="26" t="s">
-        <v>152</v>
-      </c>
-      <c r="D5" s="26" t="s">
-        <v>122</v>
-      </c>
-      <c r="E5" s="26" t="s">
-        <v>129</v>
-      </c>
-      <c r="F5" s="40" t="s">
-        <v>109</v>
-      </c>
-      <c r="G5" s="26">
+      <c r="B5" s="24" t="s">
+        <v>148</v>
+      </c>
+      <c r="C5" s="24" t="s">
+        <v>149</v>
+      </c>
+      <c r="D5" s="24" t="s">
+        <v>119</v>
+      </c>
+      <c r="E5" s="24" t="s">
+        <v>126</v>
+      </c>
+      <c r="F5" s="38" t="s">
+        <v>106</v>
+      </c>
+      <c r="G5" s="24">
         <v>3161657782</v>
       </c>
-      <c r="H5" s="26">
+      <c r="H5" s="24">
         <v>0</v>
       </c>
-      <c r="I5" s="26" t="s">
-        <v>127</v>
-      </c>
-      <c r="J5" s="26" t="str">
+      <c r="I5" s="24" t="s">
+        <v>124</v>
+      </c>
+      <c r="J5" s="24" t="str">
         <f>_xlfn.CONCAT(B5,"-",C5,"-",D5,"-",E5,"-",F5,"-",G5)</f>
         <v>Jose-Miguel-Ramirez-Perez-+57-3161657782</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A6" s="26">
+      <c r="A6" s="24">
         <v>3</v>
       </c>
-      <c r="B6" s="26" t="s">
-        <v>153</v>
-      </c>
-      <c r="C6" s="26"/>
-      <c r="D6" s="26" t="s">
-        <v>154</v>
-      </c>
-      <c r="E6" s="26" t="s">
-        <v>122</v>
-      </c>
-      <c r="F6" s="40" t="s">
-        <v>109</v>
-      </c>
-      <c r="G6" s="26">
+      <c r="B6" s="24" t="s">
+        <v>150</v>
+      </c>
+      <c r="C6" s="24"/>
+      <c r="D6" s="24" t="s">
+        <v>151</v>
+      </c>
+      <c r="E6" s="24" t="s">
+        <v>119</v>
+      </c>
+      <c r="F6" s="38" t="s">
+        <v>106</v>
+      </c>
+      <c r="G6" s="24">
         <v>3119884321</v>
       </c>
-      <c r="H6" s="26">
+      <c r="H6" s="24">
         <v>0</v>
       </c>
-      <c r="I6" s="26" t="s">
-        <v>127</v>
-      </c>
-      <c r="J6" s="26" t="str">
+      <c r="I6" s="24" t="s">
+        <v>124</v>
+      </c>
+      <c r="J6" s="24" t="str">
         <f>_xlfn.CONCAT(B6,"-",C6,"-",D6,"-",E6,"-",F6,"-",G6)</f>
         <v>Simon--Ochoa-Ramirez-+57-3119884321</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A7" s="26">
+      <c r="A7" s="24">
         <v>4</v>
       </c>
-      <c r="B7" s="26" t="s">
-        <v>155</v>
-      </c>
-      <c r="C7" s="26"/>
-      <c r="D7" s="26" t="s">
-        <v>156</v>
-      </c>
-      <c r="E7" s="26"/>
-      <c r="F7" s="40" t="s">
-        <v>157</v>
-      </c>
-      <c r="G7" s="26">
+      <c r="B7" s="24" t="s">
+        <v>152</v>
+      </c>
+      <c r="C7" s="24"/>
+      <c r="D7" s="24" t="s">
+        <v>153</v>
+      </c>
+      <c r="E7" s="24"/>
+      <c r="F7" s="38" t="s">
+        <v>154</v>
+      </c>
+      <c r="G7" s="24">
         <v>4127359182</v>
       </c>
-      <c r="H7" s="26">
+      <c r="H7" s="24">
         <v>1</v>
       </c>
-      <c r="I7" s="26" t="s">
-        <v>127</v>
-      </c>
-      <c r="J7" s="26" t="str">
+      <c r="I7" s="24" t="s">
+        <v>124</v>
+      </c>
+      <c r="J7" s="24" t="str">
         <f>_xlfn.CONCAT(B7,"-",C7,"-",D7,"-",E7,"-",F7,"-",G7)</f>
         <v>Alexis--Gallego--+58-4127359182</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A8" s="26">
+      <c r="A8" s="24">
         <v>5</v>
       </c>
-      <c r="B8" s="26" t="s">
+      <c r="B8" s="24" t="s">
+        <v>155</v>
+      </c>
+      <c r="C8" s="24" t="s">
+        <v>156</v>
+      </c>
+      <c r="D8" s="24" t="s">
+        <v>157</v>
+      </c>
+      <c r="E8" s="24" t="s">
         <v>158</v>
       </c>
-      <c r="C8" s="26" t="s">
-        <v>159</v>
-      </c>
-      <c r="D8" s="26" t="s">
-        <v>160</v>
-      </c>
-      <c r="E8" s="26" t="s">
-        <v>161</v>
-      </c>
-      <c r="F8" s="40" t="s">
+      <c r="F8" s="38" t="s">
+        <v>106</v>
+      </c>
+      <c r="G8" s="24">
+        <v>3005544332</v>
+      </c>
+      <c r="H8" s="24">
+        <v>3</v>
+      </c>
+      <c r="I8" s="24" t="s">
         <v>109</v>
       </c>
-      <c r="G8" s="26">
-        <v>3005544332</v>
-      </c>
-      <c r="H8" s="26">
-        <v>3</v>
-      </c>
-      <c r="I8" s="26" t="s">
-        <v>112</v>
-      </c>
-      <c r="J8" s="26" t="str">
+      <c r="J8" s="24" t="str">
         <f>_xlfn.CONCAT(B8,"-",C8,"-",D8,"-",E8,"-",F8,"-",G8)</f>
         <v>Kevin-Andrés-Muñoz-Salazar-+57-3005544332</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="29"/>
+      <c r="B13" s="27"/>
     </row>
     <row r="14" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="28"/>
-      <c r="B14" s="29" t="s">
+      <c r="A14" s="26"/>
+      <c r="B14" s="27" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="30"/>
-      <c r="B15" s="29" t="s">
+      <c r="A15" s="28"/>
+      <c r="B15" s="27" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="31"/>
-      <c r="B16" s="29" t="s">
+      <c r="A16" s="29"/>
+      <c r="B16" s="27" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="43"/>
-      <c r="B17" s="29" t="s">
-        <v>133</v>
+      <c r="A17" s="41"/>
+      <c r="B17" s="27" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="44"/>
-      <c r="B18" s="29" t="s">
-        <v>134</v>
+      <c r="A18" s="42"/>
+      <c r="B18" s="27" t="s">
+        <v>131</v>
       </c>
     </row>
   </sheetData>
@@ -4546,10 +4581,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="32" t="s">
+      <c r="B1" s="30" t="s">
         <v>33</v>
       </c>
     </row>
@@ -4691,7 +4726,7 @@
       <c r="K4" s="13"/>
       <c r="L4" s="13"/>
       <c r="M4" s="14" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="N4" s="13" t="s">
         <v>57</v>
@@ -4744,7 +4779,7 @@
       <c r="K5" s="13"/>
       <c r="L5" s="13"/>
       <c r="M5" s="14" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="N5" s="13" t="s">
         <v>57</v>
@@ -4780,7 +4815,7 @@
         <v>57</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="E6" s="13" t="s">
         <v>57</v>
@@ -4792,7 +4827,7 @@
       <c r="J6" s="13"/>
       <c r="K6" s="13"/>
       <c r="L6" s="13" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="M6" s="14"/>
       <c r="N6" s="13" t="s">
@@ -4812,7 +4847,7 @@
         <v>57</v>
       </c>
       <c r="T6" s="13" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="U6" s="13" t="s">
         <v>57</v>
@@ -4831,7 +4866,7 @@
         <v>57</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="E7" s="13" t="s">
         <v>55</v>
@@ -4843,10 +4878,10 @@
       <c r="J7" s="13"/>
       <c r="K7" s="13"/>
       <c r="L7" s="13" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="M7" s="14" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="N7" s="13" t="s">
         <v>57</v>
@@ -4870,19 +4905,19 @@
       </c>
     </row>
     <row r="8" spans="1:21" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="13" t="str">
-        <f>'M-HorarioBarberia'!F3</f>
-        <v>fechaCreacion</v>
-      </c>
-      <c r="B8" s="14" t="str">
-        <f>'M-HorarioBarberia'!F2</f>
-        <v>Representa la fecha en el que el dueño creo el horario para la barberia. Es dato calculado que el sistema toma la fecha de hoy cuando el dueño crea el horario</v>
+      <c r="A8" s="13" t="e">
+        <f>'M-HorarioBarberia'!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="B8" s="14" t="e">
+        <f>'M-HorarioBarberia'!#REF!</f>
+        <v>#REF!</v>
       </c>
       <c r="C8" s="13" t="s">
         <v>57</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="E8" s="13" t="s">
         <v>55</v>
@@ -4894,10 +4929,10 @@
       <c r="J8" s="13"/>
       <c r="K8" s="13"/>
       <c r="L8" s="13" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="M8" s="14" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="N8" s="13" t="s">
         <v>55</v>
@@ -4921,19 +4956,19 @@
       </c>
     </row>
     <row r="9" spans="1:21" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A9" s="13" t="str">
-        <f>'M-HorarioBarberia'!G3</f>
-        <v>fechaDesactivacion</v>
-      </c>
-      <c r="B9" s="14" t="str">
-        <f>'M-HorarioBarberia'!G2</f>
-        <v>Representa la fecha en el que el dueño decidio que este horario ya no va a ser disponible. Es un dato calculado que el sistema toma la fecha de hoy, cuando el dueño cambia el estado de vigencia</v>
+      <c r="A9" s="13" t="e">
+        <f>'M-HorarioBarberia'!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="B9" s="14" t="e">
+        <f>'M-HorarioBarberia'!#REF!</f>
+        <v>#REF!</v>
       </c>
       <c r="C9" s="13" t="s">
         <v>57</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="E9" s="13" t="s">
         <v>55</v>
@@ -4945,10 +4980,10 @@
       <c r="J9" s="13"/>
       <c r="K9" s="13"/>
       <c r="L9" s="13" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="M9" s="14" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="N9" s="13" t="s">
         <v>55</v>
@@ -4967,26 +5002,26 @@
         <v>57</v>
       </c>
       <c r="T9" s="13" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="U9" s="13" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="10" spans="1:21" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="13" t="str">
-        <f>'M-HorarioBarberia'!H3</f>
-        <v>vigente</v>
-      </c>
-      <c r="B10" s="14" t="str">
-        <f>'M-HorarioBarberia'!H2</f>
-        <v>Representa si este horario lo sigue o no usando la barberia. Una vez que el dueño cambie este estado a no vigente, no se puede volver a cambiar</v>
+      <c r="A10" s="13" t="e">
+        <f>'M-HorarioBarberia'!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="B10" s="14" t="e">
+        <f>'M-HorarioBarberia'!#REF!</f>
+        <v>#REF!</v>
       </c>
       <c r="C10" s="13" t="s">
         <v>57</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E10" s="13" t="s">
         <v>55</v>
@@ -4999,7 +5034,7 @@
       <c r="K10" s="13"/>
       <c r="L10" s="13"/>
       <c r="M10" s="14" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="N10" s="13" t="s">
         <v>57</v>
@@ -5018,7 +5053,7 @@
         <v>57</v>
       </c>
       <c r="T10" s="13" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="U10" s="13" t="s">
         <v>57</v>
@@ -5057,35 +5092,35 @@
       <c r="C12" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="D12" s="33"/>
-      <c r="E12" s="33"/>
-      <c r="F12" s="33"/>
-      <c r="G12" s="33"/>
-      <c r="H12" s="33"/>
-      <c r="I12" s="33"/>
-      <c r="J12" s="33"/>
-      <c r="K12" s="33"/>
-      <c r="L12" s="33"/>
-      <c r="M12" s="33"/>
-      <c r="N12" s="33"/>
-      <c r="O12" s="33"/>
-      <c r="P12" s="33"/>
-      <c r="Q12" s="33"/>
-      <c r="R12" s="33"/>
-      <c r="S12" s="33"/>
-      <c r="T12" s="33"/>
-      <c r="U12" s="33"/>
+      <c r="D12" s="31"/>
+      <c r="E12" s="31"/>
+      <c r="F12" s="31"/>
+      <c r="G12" s="31"/>
+      <c r="H12" s="31"/>
+      <c r="I12" s="31"/>
+      <c r="J12" s="31"/>
+      <c r="K12" s="31"/>
+      <c r="L12" s="31"/>
+      <c r="M12" s="31"/>
+      <c r="N12" s="31"/>
+      <c r="O12" s="31"/>
+      <c r="P12" s="31"/>
+      <c r="Q12" s="31"/>
+      <c r="R12" s="31"/>
+      <c r="S12" s="31"/>
+      <c r="T12" s="31"/>
+      <c r="U12" s="31"/>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A13" s="134" t="str">
-        <f>'M-HorarioBarberia'!I3</f>
+      <c r="A13" s="131" t="str">
+        <f>'M-HorarioBarberia'!F3</f>
         <v>Combinación única</v>
       </c>
-      <c r="B13" s="135" t="str">
-        <f>'M-HorarioBarberia'!I2</f>
+      <c r="B13" s="132" t="str">
+        <f>'M-HorarioBarberia'!F2</f>
         <v>Combinacion única que indica que no puede existir más de un horario con la misma barberia, dia de la semana, hora de apertura y cierre</v>
       </c>
-      <c r="C13" s="34" t="str">
+      <c r="C13" s="32" t="str">
         <f>A5</f>
         <v>diaDeLaSemana</v>
       </c>
@@ -5109,9 +5144,9 @@
       <c r="U13" s="4"/>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A14" s="134"/>
-      <c r="B14" s="134"/>
-      <c r="C14" s="34" t="str">
+      <c r="A14" s="131"/>
+      <c r="B14" s="131"/>
+      <c r="C14" s="32" t="str">
         <f>A6</f>
         <v>horaApertura</v>
       </c>
@@ -5135,9 +5170,9 @@
       <c r="U14" s="4"/>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A15" s="134"/>
-      <c r="B15" s="134"/>
-      <c r="C15" s="34" t="str">
+      <c r="A15" s="131"/>
+      <c r="B15" s="131"/>
+      <c r="C15" s="32" t="str">
         <f>A7</f>
         <v>horaCierre</v>
       </c>
@@ -5161,11 +5196,11 @@
       <c r="U15" s="4"/>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A16" s="134"/>
-      <c r="B16" s="134"/>
-      <c r="C16" s="34" t="str">
+      <c r="A16" s="131"/>
+      <c r="B16" s="131"/>
+      <c r="C16" s="32" t="e">
         <f>A8</f>
-        <v>fechaCreacion</v>
+        <v>#REF!</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="4"/>
@@ -5187,11 +5222,11 @@
       <c r="U16" s="4"/>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A17" s="134"/>
-      <c r="B17" s="134"/>
-      <c r="C17" s="34" t="str">
+      <c r="A17" s="131"/>
+      <c r="B17" s="131"/>
+      <c r="C17" s="32" t="e">
         <f>A9</f>
-        <v>fechaDesactivacion</v>
+        <v>#REF!</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="4"/>
@@ -5228,7 +5263,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="27" customWidth="1"/>
@@ -5236,13 +5271,10 @@
     <col min="3" max="3" width="39.88671875" customWidth="1"/>
     <col min="4" max="4" width="22" customWidth="1"/>
     <col min="5" max="5" width="21.5546875" customWidth="1"/>
-    <col min="6" max="6" width="26.44140625" customWidth="1"/>
-    <col min="7" max="7" width="33" customWidth="1"/>
-    <col min="8" max="8" width="28.44140625" customWidth="1"/>
-    <col min="9" max="9" width="43" customWidth="1"/>
+    <col min="6" max="6" width="43" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>1</v>
       </c>
@@ -5250,333 +5282,246 @@
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="46" t="s">
+    <row r="2" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="44" t="s">
         <v>66</v>
       </c>
-      <c r="B2" s="46" t="s">
+      <c r="B2" s="44" t="s">
+        <v>171</v>
+      </c>
+      <c r="C2" s="44" t="s">
+        <v>172</v>
+      </c>
+      <c r="D2" s="44" t="s">
+        <v>173</v>
+      </c>
+      <c r="E2" s="44" t="s">
         <v>174</v>
       </c>
-      <c r="C2" s="46" t="s">
+      <c r="F2" s="44" t="s">
         <v>175</v>
       </c>
-      <c r="D2" s="46" t="s">
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="B3" s="46" t="s">
         <v>176</v>
       </c>
-      <c r="E2" s="46" t="s">
+      <c r="C3" s="47" t="s">
         <v>177</v>
       </c>
-      <c r="F2" s="46" t="s">
+      <c r="D3" s="48" t="s">
         <v>178</v>
       </c>
-      <c r="G2" s="46" t="s">
+      <c r="E3" s="49" t="s">
         <v>179</v>
       </c>
-      <c r="H2" s="46" t="s">
-        <v>180</v>
-      </c>
-      <c r="I2" s="46" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" s="23" t="s">
-        <v>70</v>
-      </c>
-      <c r="B3" s="48" t="s">
-        <v>182</v>
-      </c>
-      <c r="C3" s="49" t="s">
-        <v>183</v>
-      </c>
-      <c r="D3" s="50" t="s">
-        <v>184</v>
-      </c>
-      <c r="E3" s="51" t="s">
-        <v>185</v>
-      </c>
-      <c r="F3" s="38" t="s">
-        <v>186</v>
-      </c>
-      <c r="G3" s="38" t="s">
-        <v>187</v>
-      </c>
-      <c r="H3" s="52" t="s">
-        <v>103</v>
-      </c>
-      <c r="I3" s="53" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" s="26">
+      <c r="F3" s="50" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="24">
         <v>1</v>
       </c>
-      <c r="B4" s="27" t="str">
+      <c r="B4" s="25" t="str">
         <f>'M-Dueño'!D4</f>
         <v>Carlos</v>
       </c>
-      <c r="C4" s="54" t="s">
-        <v>188</v>
-      </c>
-      <c r="D4" s="55">
+      <c r="C4" s="51" t="s">
+        <v>182</v>
+      </c>
+      <c r="D4" s="52">
         <v>0.375</v>
       </c>
-      <c r="E4" s="55">
+      <c r="E4" s="52">
         <v>0.79166666666666696</v>
       </c>
-      <c r="F4" s="56">
-        <v>44265</v>
-      </c>
-      <c r="G4" s="56" t="s">
-        <v>189</v>
-      </c>
-      <c r="H4" s="55" t="s">
-        <v>112</v>
-      </c>
-      <c r="I4" s="26" t="str">
-        <f t="shared" ref="I4:I10" si="0">_xlfn.CONCAT(C4,"-",TEXT(D4,"hh:mm"),"-",TEXT(E4,"hh:mm"),"-",TEXT(F4,"dd/mm/yyyy"),"-",TEXT(G4,"dd/mm/yyyy"))</f>
-        <v>Lunes-09:00-19:00-10/03/2021-1/01/1000</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A5" s="26">
+      <c r="F4" s="24" t="str">
+        <f>_xlfn.CONCAT(C4,"-",TEXT(D4,"hh:mm"),"-",TEXT(E4,"hh:mm"))</f>
+        <v>Lunes-09:00-19:00</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="24">
         <v>2</v>
       </c>
-      <c r="B5" s="27" t="str">
+      <c r="B5" s="25" t="str">
         <f>'M-Dueño'!D4</f>
         <v>Carlos</v>
       </c>
-      <c r="C5" s="26" t="s">
-        <v>190</v>
-      </c>
-      <c r="D5" s="55">
+      <c r="C5" s="24" t="s">
+        <v>184</v>
+      </c>
+      <c r="D5" s="52">
         <v>0.375</v>
       </c>
-      <c r="E5" s="55">
+      <c r="E5" s="52">
         <v>0.79166666666666696</v>
       </c>
-      <c r="F5" s="56">
-        <v>44265</v>
-      </c>
-      <c r="G5" s="56" t="s">
-        <v>189</v>
-      </c>
-      <c r="H5" s="55" t="s">
-        <v>112</v>
-      </c>
-      <c r="I5" s="26" t="str">
-        <f t="shared" si="0"/>
-        <v>Martes-09:00-19:00-10/03/2021-1/01/1000</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A6" s="26">
+      <c r="F5" s="24" t="str">
+        <f t="shared" ref="F5:F10" si="0">_xlfn.CONCAT(C5,"-",TEXT(D5,"hh:mm"),"-",TEXT(E5,"hh:mm"))</f>
+        <v>Martes-09:00-19:00</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="24">
         <v>3</v>
       </c>
-      <c r="B6" s="27" t="str">
+      <c r="B6" s="25" t="str">
         <f>'M-Dueño'!D4</f>
         <v>Carlos</v>
       </c>
-      <c r="C6" s="54" t="s">
-        <v>191</v>
-      </c>
-      <c r="D6" s="55">
+      <c r="C6" s="51" t="s">
+        <v>185</v>
+      </c>
+      <c r="D6" s="52">
         <v>0.375</v>
       </c>
-      <c r="E6" s="55">
+      <c r="E6" s="52">
         <v>0.79166666666666696</v>
       </c>
-      <c r="F6" s="56">
-        <v>44265</v>
-      </c>
-      <c r="G6" s="56" t="s">
-        <v>189</v>
-      </c>
-      <c r="H6" s="55" t="s">
-        <v>112</v>
-      </c>
-      <c r="I6" s="26" t="str">
+      <c r="F6" s="24" t="str">
         <f t="shared" si="0"/>
-        <v>Miércoles-09:00-19:00-10/03/2021-1/01/1000</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7" s="26">
+        <v>Miércoles-09:00-19:00</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="24">
         <v>4</v>
       </c>
-      <c r="B7" s="27" t="str">
+      <c r="B7" s="25" t="str">
         <f>'M-Dueño'!D4</f>
         <v>Carlos</v>
       </c>
-      <c r="C7" s="26" t="s">
-        <v>192</v>
-      </c>
-      <c r="D7" s="55">
+      <c r="C7" s="24" t="s">
+        <v>186</v>
+      </c>
+      <c r="D7" s="52">
         <v>0.375</v>
       </c>
-      <c r="E7" s="55">
+      <c r="E7" s="52">
         <v>0.79166666666666696</v>
       </c>
-      <c r="F7" s="56">
-        <v>44265</v>
-      </c>
-      <c r="G7" s="56" t="s">
-        <v>189</v>
-      </c>
-      <c r="H7" s="55" t="s">
-        <v>112</v>
-      </c>
-      <c r="I7" s="26" t="str">
+      <c r="F7" s="24" t="str">
         <f t="shared" si="0"/>
-        <v>Jueves-09:00-19:00-10/03/2021-1/01/1000</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A8" s="26">
+        <v>Jueves-09:00-19:00</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="24">
         <v>5</v>
       </c>
-      <c r="B8" s="27" t="str">
+      <c r="B8" s="25" t="str">
         <f>'M-Dueño'!D4</f>
         <v>Carlos</v>
       </c>
-      <c r="C8" s="54" t="s">
-        <v>193</v>
-      </c>
-      <c r="D8" s="55">
+      <c r="C8" s="51" t="s">
+        <v>187</v>
+      </c>
+      <c r="D8" s="52">
         <v>0.375</v>
       </c>
-      <c r="E8" s="55">
+      <c r="E8" s="52">
         <v>0.79166666666666696</v>
       </c>
-      <c r="F8" s="56">
-        <v>44265</v>
-      </c>
-      <c r="G8" s="56" t="s">
-        <v>189</v>
-      </c>
-      <c r="H8" s="55" t="s">
-        <v>112</v>
-      </c>
-      <c r="I8" s="26" t="str">
+      <c r="F8" s="24" t="str">
         <f t="shared" si="0"/>
-        <v>Viernes-09:00-19:00-10/03/2021-1/01/1000</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A9" s="26">
+        <v>Viernes-09:00-19:00</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="24">
         <v>6</v>
       </c>
-      <c r="B9" s="27" t="str">
+      <c r="B9" s="25" t="str">
         <f>'M-Dueño'!D4</f>
         <v>Carlos</v>
       </c>
-      <c r="C9" s="26" t="s">
-        <v>194</v>
-      </c>
-      <c r="D9" s="57">
+      <c r="C9" s="24" t="s">
+        <v>188</v>
+      </c>
+      <c r="D9" s="54">
         <v>0.33333333333333298</v>
       </c>
-      <c r="E9" s="55">
+      <c r="E9" s="52">
         <v>0.875</v>
       </c>
-      <c r="F9" s="56">
-        <v>45626</v>
-      </c>
-      <c r="G9" s="56">
-        <v>46023</v>
-      </c>
-      <c r="H9" s="55" t="s">
-        <v>127</v>
-      </c>
-      <c r="I9" s="26" t="str">
+      <c r="F9" s="24" t="str">
         <f t="shared" si="0"/>
-        <v>Sábado-08:00-21:00-30/11/2024-01/01/2026</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10" s="26">
+        <v>Sábado-08:00-21:00</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="24">
         <v>7</v>
       </c>
-      <c r="B10" s="27" t="str">
+      <c r="B10" s="25" t="str">
         <f>'M-Dueño'!D4</f>
         <v>Carlos</v>
       </c>
-      <c r="C10" s="54" t="s">
-        <v>195</v>
-      </c>
-      <c r="D10" s="55">
+      <c r="C10" s="51" t="s">
+        <v>189</v>
+      </c>
+      <c r="D10" s="52">
         <v>0.41666666666666702</v>
       </c>
-      <c r="E10" s="55">
+      <c r="E10" s="52">
         <v>0.625</v>
       </c>
-      <c r="F10" s="56">
-        <v>45879</v>
-      </c>
-      <c r="G10" s="56">
-        <v>46215</v>
-      </c>
-      <c r="H10" s="55" t="s">
-        <v>127</v>
-      </c>
-      <c r="I10" s="26" t="str">
+      <c r="F10" s="24" t="str">
         <f t="shared" si="0"/>
-        <v>Festivo-10:00-15:00-10/08/2025-12/07/2026</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="G14" s="58"/>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="G15" s="58"/>
-    </row>
-    <row r="16" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="28"/>
-      <c r="B16" s="29" t="s">
+        <v>Festivo-10:00-15:00</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="26"/>
+      <c r="B16" s="27" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="30"/>
-      <c r="B17" s="29" t="s">
+      <c r="A17" s="28"/>
+      <c r="B17" s="27" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="59"/>
-      <c r="B18" s="29" t="s">
-        <v>196</v>
+      <c r="A18" s="56"/>
+      <c r="B18" s="27" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="31"/>
-      <c r="B19" s="29" t="s">
+      <c r="A19" s="29"/>
+      <c r="B19" s="27" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="60"/>
-      <c r="B20" s="29" t="s">
-        <v>197</v>
+      <c r="A20" s="57"/>
+      <c r="B20" s="27" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="43"/>
-      <c r="B21" s="29" t="s">
-        <v>133</v>
+      <c r="A21" s="41"/>
+      <c r="B21" s="27" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="61"/>
-      <c r="B22" s="29" t="s">
-        <v>198</v>
+      <c r="A22" s="58"/>
+      <c r="B22" s="27" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="44"/>
-      <c r="B23" s="29" t="s">
-        <v>134</v>
+      <c r="A23" s="42"/>
+      <c r="B23" s="27" t="s">
+        <v>131</v>
       </c>
     </row>
   </sheetData>
@@ -5625,10 +5570,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="32" t="s">
+      <c r="B1" s="30" t="s">
         <v>33</v>
       </c>
     </row>
@@ -5770,7 +5715,7 @@
       <c r="K4" s="13"/>
       <c r="L4" s="13"/>
       <c r="M4" s="14" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="N4" s="13" t="s">
         <v>57</v>
@@ -5821,7 +5766,7 @@
       <c r="K5" s="13"/>
       <c r="L5" s="13"/>
       <c r="M5" s="14" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="N5" s="13" t="s">
         <v>57</v>
@@ -5871,10 +5816,10 @@
       </c>
       <c r="K6" s="13"/>
       <c r="L6" s="13" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="M6" s="14" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="N6" s="13" t="s">
         <v>57</v>
@@ -5925,7 +5870,7 @@
       <c r="K7" s="13"/>
       <c r="L7" s="13"/>
       <c r="M7" s="14" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="N7" s="13" t="s">
         <v>57</v>
@@ -5976,7 +5921,7 @@
       <c r="K8" s="13"/>
       <c r="L8" s="13"/>
       <c r="M8" s="14" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="N8" s="13" t="s">
         <v>57</v>
@@ -6028,7 +5973,7 @@
         <v>100</v>
       </c>
       <c r="L9" s="13" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="M9" s="14"/>
       <c r="N9" s="13" t="s">
@@ -6107,97 +6052,97 @@
       </c>
     </row>
     <row r="2" spans="1:7" ht="52.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="45" t="s">
+      <c r="A2" s="43" t="s">
         <v>66</v>
       </c>
-      <c r="B2" s="45" t="s">
+      <c r="B2" s="43" t="s">
+        <v>197</v>
+      </c>
+      <c r="C2" s="44" t="s">
+        <v>198</v>
+      </c>
+      <c r="D2" s="44" t="s">
+        <v>199</v>
+      </c>
+      <c r="E2" s="44" t="s">
+        <v>200</v>
+      </c>
+      <c r="F2" s="44" t="s">
+        <v>201</v>
+      </c>
+      <c r="G2" s="44" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="B3" s="59" t="s">
+        <v>176</v>
+      </c>
+      <c r="C3" s="60" t="s">
         <v>203</v>
       </c>
-      <c r="C2" s="46" t="s">
+      <c r="D3" s="60" t="s">
         <v>204</v>
       </c>
-      <c r="D2" s="46" t="s">
+      <c r="E3" s="60" t="s">
         <v>205</v>
       </c>
-      <c r="E2" s="46" t="s">
+      <c r="F3" s="60" t="s">
         <v>206</v>
       </c>
-      <c r="F2" s="46" t="s">
+      <c r="G3" s="60" t="s">
         <v>207</v>
       </c>
-      <c r="G2" s="46" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="23" t="s">
-        <v>70</v>
-      </c>
-      <c r="B3" s="62" t="s">
-        <v>182</v>
-      </c>
-      <c r="C3" s="63" t="s">
-        <v>209</v>
-      </c>
-      <c r="D3" s="63" t="s">
-        <v>210</v>
-      </c>
-      <c r="E3" s="63" t="s">
-        <v>211</v>
-      </c>
-      <c r="F3" s="63" t="s">
-        <v>212</v>
-      </c>
-      <c r="G3" s="63" t="s">
-        <v>213</v>
-      </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="26">
+      <c r="A4" s="24">
         <v>1</v>
       </c>
-      <c r="B4" s="27" t="str">
+      <c r="B4" s="25" t="str">
         <f>'M-Dueño'!D4</f>
         <v>Carlos</v>
       </c>
-      <c r="C4" s="26">
+      <c r="C4" s="24">
         <v>10</v>
       </c>
-      <c r="D4" s="64">
+      <c r="D4" s="61">
         <v>10000</v>
       </c>
-      <c r="E4" s="26">
+      <c r="E4" s="24">
         <v>3</v>
       </c>
-      <c r="F4" s="26">
+      <c r="F4" s="24">
         <v>15</v>
       </c>
-      <c r="G4" s="26">
+      <c r="G4" s="24">
         <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="28"/>
-      <c r="B9" s="29" t="s">
+      <c r="A9" s="26"/>
+      <c r="B9" s="27" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="30"/>
-      <c r="B10" s="29" t="s">
+      <c r="A10" s="28"/>
+      <c r="B10" s="27" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="59"/>
-      <c r="B11" s="29" t="s">
-        <v>196</v>
+      <c r="A11" s="56"/>
+      <c r="B11" s="27" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="65"/>
-      <c r="B12" s="29" t="s">
-        <v>214</v>
+      <c r="A12" s="62"/>
+      <c r="B12" s="27" t="s">
+        <v>208</v>
       </c>
     </row>
   </sheetData>
@@ -6240,10 +6185,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="32" t="s">
+      <c r="B1" s="30" t="s">
         <v>33</v>
       </c>
     </row>
@@ -6385,7 +6330,7 @@
       <c r="K4" s="13"/>
       <c r="L4" s="13"/>
       <c r="M4" s="14" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="N4" s="13" t="s">
         <v>57</v>
@@ -6537,10 +6482,10 @@
       </c>
       <c r="K7" s="13"/>
       <c r="L7" s="13" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="M7" s="14" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="N7" s="13" t="s">
         <v>57</v>
@@ -6576,7 +6521,7 @@
         <v>57</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E8" s="13" t="s">
         <v>55</v>
@@ -6606,7 +6551,7 @@
         <v>57</v>
       </c>
       <c r="T8" s="13" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="U8" s="13" t="s">
         <v>57</v>
@@ -6645,24 +6590,24 @@
       <c r="C10" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="D10" s="33"/>
-      <c r="E10" s="33"/>
-      <c r="F10" s="33"/>
-      <c r="G10" s="33"/>
-      <c r="H10" s="33"/>
-      <c r="I10" s="33"/>
-      <c r="J10" s="33"/>
-      <c r="K10" s="33"/>
-      <c r="L10" s="33"/>
-      <c r="M10" s="33"/>
-      <c r="N10" s="33"/>
-      <c r="O10" s="33"/>
-      <c r="P10" s="33"/>
-      <c r="Q10" s="33"/>
-      <c r="R10" s="33"/>
-      <c r="S10" s="33"/>
-      <c r="T10" s="33"/>
-      <c r="U10" s="33"/>
+      <c r="D10" s="31"/>
+      <c r="E10" s="31"/>
+      <c r="F10" s="31"/>
+      <c r="G10" s="31"/>
+      <c r="H10" s="31"/>
+      <c r="I10" s="31"/>
+      <c r="J10" s="31"/>
+      <c r="K10" s="31"/>
+      <c r="L10" s="31"/>
+      <c r="M10" s="31"/>
+      <c r="N10" s="31"/>
+      <c r="O10" s="31"/>
+      <c r="P10" s="31"/>
+      <c r="Q10" s="31"/>
+      <c r="R10" s="31"/>
+      <c r="S10" s="31"/>
+      <c r="T10" s="31"/>
+      <c r="U10" s="31"/>
     </row>
     <row r="11" spans="1:21" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="str">
@@ -6673,7 +6618,7 @@
         <f>'M-Servicio'!G2</f>
         <v>Combinacion única que indica que no puede existir más de un servicio con el mismo nombre</v>
       </c>
-      <c r="C11" s="34" t="str">
+      <c r="C11" s="32" t="str">
         <f>A5</f>
         <v>nombre</v>
       </c>
@@ -6719,203 +6664,203 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="66" t="s">
+      <c r="A1" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="66" t="s">
+      <c r="B1" s="63" t="s">
         <v>33</v>
       </c>
-      <c r="D1" s="66"/>
-      <c r="E1" s="67"/>
-      <c r="F1" s="67"/>
-      <c r="G1" s="22"/>
+      <c r="D1" s="63"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="20"/>
     </row>
     <row r="2" spans="1:7" ht="52.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="45" t="s">
+      <c r="A2" s="43" t="s">
         <v>66</v>
       </c>
-      <c r="B2" s="45" t="s">
+      <c r="B2" s="43" t="s">
+        <v>209</v>
+      </c>
+      <c r="C2" s="43" t="s">
+        <v>210</v>
+      </c>
+      <c r="D2" s="43" t="s">
+        <v>211</v>
+      </c>
+      <c r="E2" s="65" t="s">
+        <v>212</v>
+      </c>
+      <c r="F2" s="65" t="s">
+        <v>213</v>
+      </c>
+      <c r="G2" s="44" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="66" t="s">
+        <v>70</v>
+      </c>
+      <c r="B3" s="67" t="s">
+        <v>176</v>
+      </c>
+      <c r="C3" s="68" t="s">
+        <v>73</v>
+      </c>
+      <c r="D3" s="68" t="s">
         <v>215</v>
       </c>
-      <c r="C2" s="45" t="s">
+      <c r="E3" s="69" t="s">
         <v>216</v>
       </c>
-      <c r="D2" s="45" t="s">
+      <c r="F3" s="70" t="s">
         <v>217</v>
       </c>
-      <c r="E2" s="68" t="s">
+      <c r="G3" s="71" t="s">
         <v>218</v>
       </c>
-      <c r="F2" s="68" t="s">
-        <v>219</v>
-      </c>
-      <c r="G2" s="46" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="69" t="s">
-        <v>70</v>
-      </c>
-      <c r="B3" s="70" t="s">
-        <v>182</v>
-      </c>
-      <c r="C3" s="71" t="s">
-        <v>73</v>
-      </c>
-      <c r="D3" s="71" t="s">
-        <v>221</v>
-      </c>
-      <c r="E3" s="72" t="s">
-        <v>222</v>
-      </c>
-      <c r="F3" s="73" t="s">
-        <v>223</v>
-      </c>
-      <c r="G3" s="74" t="s">
-        <v>224</v>
-      </c>
     </row>
     <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="75">
+      <c r="A4" s="72">
         <v>1</v>
       </c>
-      <c r="B4" s="76" t="str">
+      <c r="B4" s="73" t="str">
         <f>'M-Dueño'!D4</f>
         <v>Carlos</v>
       </c>
-      <c r="C4" s="75" t="s">
-        <v>225</v>
-      </c>
-      <c r="D4" s="77" t="s">
-        <v>226</v>
-      </c>
-      <c r="E4" s="78">
+      <c r="C4" s="72" t="s">
+        <v>219</v>
+      </c>
+      <c r="D4" s="74" t="s">
+        <v>220</v>
+      </c>
+      <c r="E4" s="75">
         <v>22000</v>
       </c>
-      <c r="F4" s="78" t="s">
-        <v>112</v>
-      </c>
-      <c r="G4" s="26" t="str">
+      <c r="F4" s="75" t="s">
+        <v>109</v>
+      </c>
+      <c r="G4" s="24" t="str">
         <f>C4</f>
         <v>Motilada</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="75">
+      <c r="A5" s="72">
         <v>2</v>
       </c>
-      <c r="B5" s="79" t="str">
+      <c r="B5" s="76" t="str">
         <f>'M-Dueño'!D4</f>
         <v>Carlos</v>
       </c>
-      <c r="C5" s="75" t="s">
-        <v>227</v>
-      </c>
-      <c r="D5" s="77" t="s">
-        <v>228</v>
-      </c>
-      <c r="E5" s="78">
+      <c r="C5" s="72" t="s">
+        <v>221</v>
+      </c>
+      <c r="D5" s="74" t="s">
+        <v>222</v>
+      </c>
+      <c r="E5" s="75">
         <v>12000</v>
       </c>
-      <c r="F5" s="78" t="s">
-        <v>112</v>
-      </c>
-      <c r="G5" s="26" t="str">
+      <c r="F5" s="75" t="s">
+        <v>109</v>
+      </c>
+      <c r="G5" s="24" t="str">
         <f>C5</f>
         <v>Corte de barba</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="75">
+      <c r="A6" s="72">
         <v>3</v>
       </c>
-      <c r="B6" s="79" t="str">
+      <c r="B6" s="76" t="str">
         <f>'M-Dueño'!D4</f>
         <v>Carlos</v>
       </c>
-      <c r="C6" s="75" t="s">
-        <v>229</v>
-      </c>
-      <c r="D6" s="77" t="s">
-        <v>230</v>
-      </c>
-      <c r="E6" s="78">
+      <c r="C6" s="72" t="s">
+        <v>223</v>
+      </c>
+      <c r="D6" s="74" t="s">
+        <v>224</v>
+      </c>
+      <c r="E6" s="75">
         <v>15000</v>
       </c>
-      <c r="F6" s="78" t="s">
-        <v>112</v>
-      </c>
-      <c r="G6" s="26" t="str">
+      <c r="F6" s="75" t="s">
+        <v>109</v>
+      </c>
+      <c r="G6" s="24" t="str">
         <f>C6</f>
         <v>Perfilada de barba</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="75">
+      <c r="A7" s="72">
         <v>4</v>
       </c>
-      <c r="B7" s="79" t="str">
+      <c r="B7" s="76" t="str">
         <f>'M-Dueño'!D4</f>
         <v>Carlos</v>
       </c>
-      <c r="C7" s="77" t="s">
-        <v>231</v>
-      </c>
-      <c r="D7" s="77" t="s">
-        <v>232</v>
-      </c>
-      <c r="E7" s="78">
+      <c r="C7" s="74" t="s">
+        <v>225</v>
+      </c>
+      <c r="D7" s="74" t="s">
+        <v>226</v>
+      </c>
+      <c r="E7" s="75">
         <v>35000</v>
       </c>
-      <c r="F7" s="78" t="s">
-        <v>112</v>
-      </c>
-      <c r="G7" s="80" t="str">
+      <c r="F7" s="75" t="s">
+        <v>109</v>
+      </c>
+      <c r="G7" s="77" t="str">
         <f>C7</f>
         <v>Arreglo completo de barba con toalla caliente</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="28"/>
-      <c r="B13" s="29" t="s">
+      <c r="A13" s="26"/>
+      <c r="B13" s="27" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="30"/>
-      <c r="B14" s="29" t="s">
+      <c r="A14" s="28"/>
+      <c r="B14" s="27" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="59"/>
-      <c r="B15" s="29" t="s">
-        <v>233</v>
+      <c r="A15" s="56"/>
+      <c r="B15" s="27" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="31"/>
-      <c r="B16" s="29" t="s">
+      <c r="A16" s="29"/>
+      <c r="B16" s="27" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="81"/>
-      <c r="B17" s="29" t="s">
-        <v>214</v>
+      <c r="A17" s="78"/>
+      <c r="B17" s="27" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="61"/>
-      <c r="B18" s="29" t="s">
-        <v>198</v>
+      <c r="A18" s="58"/>
+      <c r="B18" s="27" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="82"/>
-      <c r="B19" s="29" t="s">
-        <v>134</v>
+      <c r="A19" s="79"/>
+      <c r="B19" s="27" t="s">
+        <v>131</v>
       </c>
     </row>
   </sheetData>
@@ -6961,10 +6906,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="32" t="s">
+      <c r="B1" s="30" t="s">
         <v>33</v>
       </c>
     </row>
@@ -7106,7 +7051,7 @@
       <c r="K4" s="13"/>
       <c r="L4" s="13"/>
       <c r="M4" s="14" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="N4" s="13" t="s">
         <v>57</v>
@@ -7155,7 +7100,7 @@
       <c r="K5" s="13"/>
       <c r="L5" s="13"/>
       <c r="M5" s="14" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="N5" s="13" t="s">
         <v>57</v>
@@ -7205,10 +7150,10 @@
       </c>
       <c r="K6" s="13"/>
       <c r="L6" s="13" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="M6" s="14" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="N6" s="13" t="s">
         <v>57</v>
@@ -7258,7 +7203,7 @@
       </c>
       <c r="K7" s="13"/>
       <c r="L7" s="13" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="M7" s="14"/>
       <c r="N7" s="13" t="s">
@@ -7317,35 +7262,35 @@
       <c r="C9" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="D9" s="33"/>
-      <c r="E9" s="33"/>
-      <c r="F9" s="33"/>
-      <c r="G9" s="33"/>
-      <c r="H9" s="33"/>
-      <c r="I9" s="33"/>
-      <c r="J9" s="33"/>
-      <c r="K9" s="33"/>
-      <c r="L9" s="33"/>
-      <c r="M9" s="33"/>
-      <c r="N9" s="33"/>
-      <c r="O9" s="33"/>
-      <c r="P9" s="33"/>
-      <c r="Q9" s="33"/>
-      <c r="R9" s="33"/>
-      <c r="S9" s="33"/>
-      <c r="T9" s="33"/>
-      <c r="U9" s="33"/>
+      <c r="D9" s="31"/>
+      <c r="E9" s="31"/>
+      <c r="F9" s="31"/>
+      <c r="G9" s="31"/>
+      <c r="H9" s="31"/>
+      <c r="I9" s="31"/>
+      <c r="J9" s="31"/>
+      <c r="K9" s="31"/>
+      <c r="L9" s="31"/>
+      <c r="M9" s="31"/>
+      <c r="N9" s="31"/>
+      <c r="O9" s="31"/>
+      <c r="P9" s="31"/>
+      <c r="Q9" s="31"/>
+      <c r="R9" s="31"/>
+      <c r="S9" s="31"/>
+      <c r="T9" s="31"/>
+      <c r="U9" s="31"/>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A10" s="134" t="str">
+      <c r="A10" s="131" t="str">
         <f>'M-BarberoServicio'!F3</f>
         <v>Combinación única</v>
       </c>
-      <c r="B10" s="135" t="str">
+      <c r="B10" s="132" t="str">
         <f>'M-BarberoServicio'!F2</f>
         <v>Combinación única que indica que un mismo barbero no puede aparecer dos veces ofreciendo el mismo servicio</v>
       </c>
-      <c r="C10" s="34" t="str">
+      <c r="C10" s="32" t="str">
         <f>A4</f>
         <v>barbero</v>
       </c>
@@ -7369,9 +7314,9 @@
       <c r="U10" s="4"/>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A11" s="134"/>
-      <c r="B11" s="134"/>
-      <c r="C11" s="34" t="str">
+      <c r="A11" s="131"/>
+      <c r="B11" s="131"/>
+      <c r="C11" s="32" t="str">
         <f>A5</f>
         <v>servicio</v>
       </c>
@@ -7428,295 +7373,295 @@
       </c>
     </row>
     <row r="2" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="45" t="s">
+      <c r="A2" s="43" t="s">
         <v>66</v>
       </c>
-      <c r="B2" s="83" t="s">
+      <c r="B2" s="80" t="s">
+        <v>230</v>
+      </c>
+      <c r="C2" s="65" t="s">
+        <v>231</v>
+      </c>
+      <c r="D2" s="65" t="s">
+        <v>232</v>
+      </c>
+      <c r="E2" s="65" t="s">
+        <v>233</v>
+      </c>
+      <c r="F2" s="44" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="B3" s="46" t="s">
+        <v>235</v>
+      </c>
+      <c r="C3" s="46" t="s">
         <v>236</v>
       </c>
-      <c r="C2" s="68" t="s">
+      <c r="D3" s="81" t="s">
         <v>237</v>
       </c>
-      <c r="D2" s="68" t="s">
+      <c r="E3" s="81" t="s">
         <v>238</v>
       </c>
-      <c r="E2" s="68" t="s">
-        <v>239</v>
-      </c>
-      <c r="F2" s="46" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="23" t="s">
-        <v>70</v>
-      </c>
-      <c r="B3" s="48" t="s">
-        <v>241</v>
-      </c>
-      <c r="C3" s="48" t="s">
-        <v>242</v>
-      </c>
-      <c r="D3" s="84" t="s">
-        <v>243</v>
-      </c>
-      <c r="E3" s="84" t="s">
-        <v>244</v>
-      </c>
-      <c r="F3" s="85" t="s">
-        <v>149</v>
+      <c r="F3" s="82" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="26">
+      <c r="A4" s="24">
         <v>1</v>
       </c>
-      <c r="B4" s="27" t="str">
+      <c r="B4" s="25" t="str">
         <f>_xlfn.CONCAT('M-Barbero'!B4," ",'M-Barbero'!D4)</f>
         <v>Juan García</v>
       </c>
-      <c r="C4" s="27" t="str">
+      <c r="C4" s="25" t="str">
         <f>'M-Servicio'!C4</f>
         <v>Motilada</v>
       </c>
-      <c r="D4" s="41">
+      <c r="D4" s="39">
         <v>45</v>
       </c>
-      <c r="E4" s="41">
+      <c r="E4" s="39">
         <v>15</v>
       </c>
-      <c r="F4" s="26" t="str">
+      <c r="F4" s="24" t="str">
         <f t="shared" ref="F4:F12" si="0">_xlfn.CONCAT(B4,"-",C4)</f>
         <v>Juan García-Motilada</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="26">
+      <c r="A5" s="24">
         <v>2</v>
       </c>
-      <c r="B5" s="27" t="str">
+      <c r="B5" s="25" t="str">
         <f>_xlfn.CONCAT('M-Barbero'!B5," ",'M-Barbero'!D5)</f>
         <v>Juan Ortiz</v>
       </c>
-      <c r="C5" s="27" t="str">
+      <c r="C5" s="25" t="str">
         <f>'M-Servicio'!C5</f>
         <v>Corte de barba</v>
       </c>
-      <c r="D5" s="41">
+      <c r="D5" s="39">
         <v>10</v>
       </c>
-      <c r="E5" s="41">
+      <c r="E5" s="39">
         <v>5</v>
       </c>
-      <c r="F5" s="26" t="str">
+      <c r="F5" s="24" t="str">
         <f t="shared" si="0"/>
         <v>Juan Ortiz-Corte de barba</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="26">
+      <c r="A6" s="24">
         <v>3</v>
       </c>
-      <c r="B6" s="27" t="str">
+      <c r="B6" s="25" t="str">
         <f>_xlfn.CONCAT('M-Barbero'!B6," ",'M-Barbero'!D6)</f>
         <v>Carlos Arbeladez</v>
       </c>
-      <c r="C6" s="27" t="str">
+      <c r="C6" s="25" t="str">
         <f>'M-Servicio'!C6</f>
         <v>Perfilada de barba</v>
       </c>
-      <c r="D6" s="41">
+      <c r="D6" s="39">
         <v>15</v>
       </c>
-      <c r="E6" s="41">
+      <c r="E6" s="39">
         <v>5</v>
       </c>
-      <c r="F6" s="26" t="str">
+      <c r="F6" s="24" t="str">
         <f t="shared" si="0"/>
         <v>Carlos Arbeladez-Perfilada de barba</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="26">
+      <c r="A7" s="24">
         <v>4</v>
       </c>
-      <c r="B7" s="27" t="str">
+      <c r="B7" s="25" t="str">
         <f>_xlfn.CONCAT('M-Barbero'!B7," ",'M-Barbero'!D7)</f>
         <v>Andres Ramirez</v>
       </c>
-      <c r="C7" s="27" t="str">
+      <c r="C7" s="25" t="str">
         <f>'M-Servicio'!C7</f>
         <v>Arreglo completo de barba con toalla caliente</v>
       </c>
-      <c r="D7" s="41">
+      <c r="D7" s="39">
         <v>40</v>
       </c>
-      <c r="E7" s="41">
+      <c r="E7" s="39">
         <v>10</v>
       </c>
-      <c r="F7" s="26" t="str">
+      <c r="F7" s="24" t="str">
         <f t="shared" si="0"/>
         <v>Andres Ramirez-Arreglo completo de barba con toalla caliente</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="26">
+      <c r="A8" s="24">
         <v>5</v>
       </c>
-      <c r="B8" s="27" t="str">
+      <c r="B8" s="25" t="str">
         <f>_xlfn.CONCAT('M-Barbero'!B5," ",'M-Barbero'!D5)</f>
         <v>Juan Ortiz</v>
       </c>
-      <c r="C8" s="27" t="str">
+      <c r="C8" s="25" t="str">
         <f>'M-Servicio'!C4</f>
         <v>Motilada</v>
       </c>
-      <c r="D8" s="41">
+      <c r="D8" s="39">
         <v>40</v>
       </c>
-      <c r="E8" s="41">
+      <c r="E8" s="39">
         <v>10</v>
       </c>
-      <c r="F8" s="26" t="str">
+      <c r="F8" s="24" t="str">
         <f t="shared" si="0"/>
         <v>Juan Ortiz-Motilada</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="26">
+      <c r="A9" s="24">
         <v>6</v>
       </c>
-      <c r="B9" s="27" t="str">
+      <c r="B9" s="25" t="str">
         <f>_xlfn.CONCAT('M-Barbero'!B6," ",'M-Barbero'!D6)</f>
         <v>Carlos Arbeladez</v>
       </c>
-      <c r="C9" s="27" t="str">
+      <c r="C9" s="25" t="str">
         <f>'M-Servicio'!C5</f>
         <v>Corte de barba</v>
       </c>
-      <c r="D9" s="41">
+      <c r="D9" s="39">
         <v>15</v>
       </c>
-      <c r="E9" s="41">
+      <c r="E9" s="39">
         <v>5</v>
       </c>
-      <c r="F9" s="26" t="str">
+      <c r="F9" s="24" t="str">
         <f t="shared" si="0"/>
         <v>Carlos Arbeladez-Corte de barba</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="26">
+      <c r="A10" s="24">
         <v>7</v>
       </c>
-      <c r="B10" s="27" t="str">
+      <c r="B10" s="25" t="str">
         <f>_xlfn.CONCAT('M-Barbero'!B4," ",'M-Barbero'!D4)</f>
         <v>Juan García</v>
       </c>
-      <c r="C10" s="27" t="str">
+      <c r="C10" s="25" t="str">
         <f>'M-Servicio'!C6</f>
         <v>Perfilada de barba</v>
       </c>
-      <c r="D10" s="41">
+      <c r="D10" s="39">
         <v>20</v>
       </c>
-      <c r="E10" s="41">
+      <c r="E10" s="39">
         <v>5</v>
       </c>
-      <c r="F10" s="26" t="str">
+      <c r="F10" s="24" t="str">
         <f t="shared" si="0"/>
         <v>Juan García-Perfilada de barba</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="26">
+      <c r="A11" s="24">
         <v>8</v>
       </c>
-      <c r="B11" s="27" t="str">
+      <c r="B11" s="25" t="str">
         <f>_xlfn.CONCAT('M-Barbero'!B7," ",'M-Barbero'!D7)</f>
         <v>Andres Ramirez</v>
       </c>
-      <c r="C11" s="27" t="str">
+      <c r="C11" s="25" t="str">
         <f>'M-Servicio'!C4</f>
         <v>Motilada</v>
       </c>
-      <c r="D11" s="41">
+      <c r="D11" s="39">
         <v>50</v>
       </c>
-      <c r="E11" s="41">
+      <c r="E11" s="39">
         <v>15</v>
       </c>
-      <c r="F11" s="26" t="str">
+      <c r="F11" s="24" t="str">
         <f t="shared" si="0"/>
         <v>Andres Ramirez-Motilada</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="26">
+      <c r="A12" s="24">
         <v>9</v>
       </c>
-      <c r="B12" s="27" t="str">
+      <c r="B12" s="25" t="str">
         <f>_xlfn.CONCAT('M-Barbero'!B8," ",'M-Barbero'!D8)</f>
         <v>Juan Zambrano</v>
       </c>
-      <c r="C12" s="27" t="str">
+      <c r="C12" s="25" t="str">
         <f>'M-Servicio'!C5</f>
         <v>Corte de barba</v>
       </c>
-      <c r="D12" s="41">
+      <c r="D12" s="39">
         <v>12</v>
       </c>
-      <c r="E12" s="41">
+      <c r="E12" s="39">
         <v>5</v>
       </c>
-      <c r="F12" s="26" t="str">
+      <c r="F12" s="24" t="str">
         <f t="shared" si="0"/>
         <v>Juan Zambrano-Corte de barba</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="29"/>
+      <c r="B13" s="27"/>
     </row>
     <row r="14" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="29"/>
+      <c r="B14" s="27"/>
     </row>
     <row r="15" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="29"/>
+      <c r="B15" s="27"/>
     </row>
     <row r="16" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="29"/>
+      <c r="B16" s="27"/>
     </row>
     <row r="17" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="29"/>
+      <c r="B17" s="27"/>
     </row>
     <row r="18" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="28"/>
-      <c r="B18" s="29" t="s">
+      <c r="A18" s="26"/>
+      <c r="B18" s="27" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="30"/>
-      <c r="B19" s="29" t="s">
+      <c r="A19" s="28"/>
+      <c r="B19" s="27" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="59"/>
-      <c r="B20" s="29" t="s">
-        <v>233</v>
+      <c r="A20" s="56"/>
+      <c r="B20" s="27" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="81"/>
-      <c r="B21" s="29" t="s">
-        <v>214</v>
+      <c r="A21" s="78"/>
+      <c r="B21" s="27" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="82"/>
-      <c r="B22" s="29" t="s">
-        <v>134</v>
+      <c r="A22" s="79"/>
+      <c r="B22" s="27" t="s">
+        <v>131</v>
       </c>
     </row>
   </sheetData>
@@ -7767,10 +7712,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="32" t="s">
+      <c r="B1" s="30" t="s">
         <v>33</v>
       </c>
     </row>
@@ -7912,7 +7857,7 @@
       <c r="K4" s="13"/>
       <c r="L4" s="13"/>
       <c r="M4" s="14" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="N4" s="13" t="s">
         <v>57</v>
@@ -7965,7 +7910,7 @@
       <c r="K5" s="13"/>
       <c r="L5" s="13"/>
       <c r="M5" s="14" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="N5" s="13" t="s">
         <v>57</v>
@@ -8001,7 +7946,7 @@
         <v>57</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="E6" s="13" t="s">
         <v>57</v>
@@ -8013,10 +7958,10 @@
       <c r="J6" s="13"/>
       <c r="K6" s="13"/>
       <c r="L6" s="13" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="M6" s="14" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="N6" s="13" t="s">
         <v>57</v>
@@ -8035,7 +7980,7 @@
         <v>57</v>
       </c>
       <c r="T6" s="13" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="U6" s="13" t="s">
         <v>57</v>
@@ -8054,7 +7999,7 @@
         <v>57</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="E7" s="13" t="s">
         <v>55</v>
@@ -8066,10 +8011,10 @@
       <c r="J7" s="13"/>
       <c r="K7" s="13"/>
       <c r="L7" s="13" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="M7" s="14" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="N7" s="13" t="s">
         <v>57</v>
@@ -8105,7 +8050,7 @@
         <v>57</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="E8" s="13" t="s">
         <v>55</v>
@@ -8117,10 +8062,10 @@
       <c r="J8" s="13"/>
       <c r="K8" s="13"/>
       <c r="L8" s="13" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="M8" s="14" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="N8" s="13" t="s">
         <v>55</v>
@@ -8156,7 +8101,7 @@
         <v>57</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="E9" s="13" t="s">
         <v>55</v>
@@ -8168,10 +8113,10 @@
       <c r="J9" s="13"/>
       <c r="K9" s="13"/>
       <c r="L9" s="13" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="M9" s="14" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="N9" s="13" t="s">
         <v>55</v>
@@ -8190,7 +8135,7 @@
         <v>57</v>
       </c>
       <c r="T9" s="13" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="U9" s="13" t="s">
         <v>57</v>
@@ -8209,7 +8154,7 @@
         <v>57</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E10" s="13" t="s">
         <v>55</v>
@@ -8222,7 +8167,7 @@
       <c r="K10" s="13"/>
       <c r="L10" s="13"/>
       <c r="M10" s="14" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="N10" s="13" t="s">
         <v>57</v>
@@ -8241,7 +8186,7 @@
         <v>57</v>
       </c>
       <c r="T10" s="13" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="U10" s="13" t="s">
         <v>57</v>
@@ -8280,35 +8225,35 @@
       <c r="C12" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="D12" s="33"/>
-      <c r="E12" s="33"/>
-      <c r="F12" s="33"/>
-      <c r="G12" s="33"/>
-      <c r="H12" s="33"/>
-      <c r="I12" s="33"/>
-      <c r="J12" s="33"/>
-      <c r="K12" s="33"/>
-      <c r="L12" s="33"/>
-      <c r="M12" s="33"/>
-      <c r="N12" s="33"/>
-      <c r="O12" s="33"/>
-      <c r="P12" s="33"/>
-      <c r="Q12" s="33"/>
-      <c r="R12" s="33"/>
-      <c r="S12" s="33"/>
-      <c r="T12" s="33"/>
-      <c r="U12" s="33"/>
+      <c r="D12" s="31"/>
+      <c r="E12" s="31"/>
+      <c r="F12" s="31"/>
+      <c r="G12" s="31"/>
+      <c r="H12" s="31"/>
+      <c r="I12" s="31"/>
+      <c r="J12" s="31"/>
+      <c r="K12" s="31"/>
+      <c r="L12" s="31"/>
+      <c r="M12" s="31"/>
+      <c r="N12" s="31"/>
+      <c r="O12" s="31"/>
+      <c r="P12" s="31"/>
+      <c r="Q12" s="31"/>
+      <c r="R12" s="31"/>
+      <c r="S12" s="31"/>
+      <c r="T12" s="31"/>
+      <c r="U12" s="31"/>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A13" s="134" t="str">
+      <c r="A13" s="131" t="str">
         <f>'M-HorarioBarbero'!J3</f>
         <v>Combinación única</v>
       </c>
-      <c r="B13" s="135" t="str">
+      <c r="B13" s="132" t="str">
         <f>'M-HorarioBarbero'!J2</f>
         <v>Combinación única que indica que un barbero no puede tener más de una agenda, cada barbero organiza todo su tiempo en un único lugar</v>
       </c>
-      <c r="C13" s="34" t="str">
+      <c r="C13" s="32" t="str">
         <f t="shared" ref="C13:C18" si="0">A4</f>
         <v>barbero</v>
       </c>
@@ -8332,9 +8277,9 @@
       <c r="U13" s="4"/>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A14" s="134"/>
-      <c r="B14" s="134"/>
-      <c r="C14" s="34" t="str">
+      <c r="A14" s="131"/>
+      <c r="B14" s="131"/>
+      <c r="C14" s="32" t="str">
         <f t="shared" si="0"/>
         <v>diaDeLaSemana</v>
       </c>
@@ -8358,9 +8303,9 @@
       <c r="U14" s="4"/>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A15" s="134"/>
-      <c r="B15" s="134"/>
-      <c r="C15" s="34" t="str">
+      <c r="A15" s="131"/>
+      <c r="B15" s="131"/>
+      <c r="C15" s="32" t="str">
         <f t="shared" si="0"/>
         <v>horaInicio</v>
       </c>
@@ -8384,9 +8329,9 @@
       <c r="U15" s="4"/>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A16" s="134"/>
-      <c r="B16" s="134"/>
-      <c r="C16" s="34" t="str">
+      <c r="A16" s="131"/>
+      <c r="B16" s="131"/>
+      <c r="C16" s="32" t="str">
         <f t="shared" si="0"/>
         <v>horaFinal</v>
       </c>
@@ -8410,9 +8355,9 @@
       <c r="U16" s="4"/>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A17" s="134"/>
-      <c r="B17" s="134"/>
-      <c r="C17" s="34" t="str">
+      <c r="A17" s="131"/>
+      <c r="B17" s="131"/>
+      <c r="C17" s="32" t="str">
         <f t="shared" si="0"/>
         <v>fechaCreacion</v>
       </c>
@@ -8436,9 +8381,9 @@
       <c r="U17" s="4"/>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A18" s="134"/>
-      <c r="B18" s="134"/>
-      <c r="C18" s="34" t="str">
+      <c r="A18" s="131"/>
+      <c r="B18" s="131"/>
+      <c r="C18" s="32" t="str">
         <f t="shared" si="0"/>
         <v>fechaDesactivacion</v>
       </c>
@@ -8905,271 +8850,271 @@
       <c r="I1" s="5"/>
     </row>
     <row r="2" spans="1:10" ht="69" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="45" t="s">
+      <c r="A2" s="43" t="s">
         <v>66</v>
       </c>
-      <c r="B2" s="45" t="s">
+      <c r="B2" s="43" t="s">
+        <v>243</v>
+      </c>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43" t="s">
+        <v>244</v>
+      </c>
+      <c r="E2" s="43" t="s">
+        <v>245</v>
+      </c>
+      <c r="F2" s="43" t="s">
+        <v>246</v>
+      </c>
+      <c r="G2" s="43" t="s">
+        <v>247</v>
+      </c>
+      <c r="H2" s="43" t="s">
+        <v>248</v>
+      </c>
+      <c r="I2" s="43" t="s">
         <v>249</v>
       </c>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45" t="s">
+      <c r="J2" s="44" t="s">
         <v>250</v>
       </c>
-      <c r="E2" s="45" t="s">
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="B3" s="83" t="s">
+        <v>235</v>
+      </c>
+      <c r="C3" s="46" t="s">
+        <v>266</v>
+      </c>
+      <c r="D3" s="84" t="s">
+        <v>177</v>
+      </c>
+      <c r="E3" s="85" t="s">
         <v>251</v>
       </c>
-      <c r="F2" s="45" t="s">
+      <c r="F3" s="85" t="s">
         <v>252</v>
       </c>
-      <c r="G2" s="45" t="s">
-        <v>253</v>
-      </c>
-      <c r="H2" s="45" t="s">
-        <v>254</v>
-      </c>
-      <c r="I2" s="45" t="s">
-        <v>255</v>
-      </c>
-      <c r="J2" s="46" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A3" s="23" t="s">
-        <v>70</v>
-      </c>
-      <c r="B3" s="86" t="s">
-        <v>241</v>
-      </c>
-      <c r="C3" s="48" t="s">
-        <v>272</v>
-      </c>
-      <c r="D3" s="87" t="s">
-        <v>183</v>
-      </c>
-      <c r="E3" s="88" t="s">
-        <v>257</v>
-      </c>
-      <c r="F3" s="88" t="s">
-        <v>258</v>
-      </c>
-      <c r="G3" s="89" t="s">
-        <v>186</v>
-      </c>
-      <c r="H3" s="89" t="s">
-        <v>187</v>
-      </c>
-      <c r="I3" s="90" t="s">
-        <v>103</v>
-      </c>
-      <c r="J3" s="74" t="s">
-        <v>149</v>
+      <c r="G3" s="86" t="s">
+        <v>180</v>
+      </c>
+      <c r="H3" s="86" t="s">
+        <v>181</v>
+      </c>
+      <c r="I3" s="87" t="s">
+        <v>100</v>
+      </c>
+      <c r="J3" s="71" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="26">
+      <c r="A4" s="24">
         <v>1</v>
       </c>
-      <c r="B4" s="91" t="str">
+      <c r="B4" s="88" t="str">
         <f>'M-Barbero'!K4</f>
         <v>Juan-Fernando-García-Lopez-+57-3245627890</v>
       </c>
-      <c r="C4" s="91"/>
-      <c r="D4" s="54" t="s">
-        <v>188</v>
-      </c>
-      <c r="E4" s="55">
+      <c r="C4" s="88"/>
+      <c r="D4" s="51" t="s">
+        <v>182</v>
+      </c>
+      <c r="E4" s="52">
         <v>0.41666666666666702</v>
       </c>
-      <c r="F4" s="55">
+      <c r="F4" s="52">
         <v>0.66666666666666696</v>
       </c>
-      <c r="G4" s="56">
+      <c r="G4" s="53">
         <v>45780</v>
       </c>
-      <c r="H4" s="56" t="s">
-        <v>189</v>
-      </c>
-      <c r="I4" s="55" t="s">
-        <v>112</v>
-      </c>
-      <c r="J4" s="80" t="str">
+      <c r="H4" s="53" t="s">
+        <v>183</v>
+      </c>
+      <c r="I4" s="52" t="s">
+        <v>109</v>
+      </c>
+      <c r="J4" s="77" t="str">
         <f>_xlfn.CONCAT(B4,"-",D4,"-",TEXT(E4,"hh:mm"),"-",TEXT(F4,"hh:mm"),"-",TEXT(G4,"dd/mm/yyyy"),"-",TEXT(H4,"dd/mm/yyyy"))</f>
         <v>Juan-Fernando-García-Lopez-+57-3245627890-Lunes-10:00-16:00-03/05/2025-1/01/1000</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="26">
+      <c r="A5" s="24">
         <v>2</v>
       </c>
-      <c r="B5" s="91" t="str">
+      <c r="B5" s="88" t="str">
         <f>'M-Barbero'!K5</f>
         <v>Juan-David-Ortiz-Sanchez-+57-3124518923</v>
       </c>
-      <c r="C5" s="91"/>
-      <c r="D5" s="26" t="s">
-        <v>190</v>
-      </c>
-      <c r="E5" s="55">
+      <c r="C5" s="88"/>
+      <c r="D5" s="24" t="s">
+        <v>184</v>
+      </c>
+      <c r="E5" s="52">
         <v>0.375</v>
       </c>
-      <c r="F5" s="55">
+      <c r="F5" s="52">
         <v>0.625</v>
       </c>
-      <c r="G5" s="56">
+      <c r="G5" s="53">
         <v>45718</v>
       </c>
-      <c r="H5" s="56" t="s">
-        <v>189</v>
-      </c>
-      <c r="I5" s="55" t="s">
-        <v>112</v>
-      </c>
-      <c r="J5" s="80" t="str">
+      <c r="H5" s="53" t="s">
+        <v>183</v>
+      </c>
+      <c r="I5" s="52" t="s">
+        <v>109</v>
+      </c>
+      <c r="J5" s="77" t="str">
         <f>_xlfn.CONCAT(B5,"-",D5,"-",TEXT(E5,"hh:mm"),"-",TEXT(F5,"hh:mm"),"-",TEXT(G5,"dd/mm/yyyy"),"-",TEXT(H5,"dd/mm/yyyy"))</f>
         <v>Juan-David-Ortiz-Sanchez-+57-3124518923-Martes-09:00-15:00-02/03/2025-1/01/1000</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="26">
+      <c r="A6" s="24">
         <v>3</v>
       </c>
-      <c r="B6" s="91" t="str">
+      <c r="B6" s="88" t="str">
         <f>'M-Barbero'!K6</f>
         <v>Carlos--Arbeladez--+57-3214533321</v>
       </c>
-      <c r="C6" s="91"/>
-      <c r="D6" s="26" t="s">
-        <v>192</v>
-      </c>
-      <c r="E6" s="55">
+      <c r="C6" s="88"/>
+      <c r="D6" s="24" t="s">
+        <v>186</v>
+      </c>
+      <c r="E6" s="52">
         <v>0.54166666666666696</v>
       </c>
-      <c r="F6" s="55">
+      <c r="F6" s="52">
         <v>0.79166666666666696</v>
       </c>
-      <c r="G6" s="56">
+      <c r="G6" s="53">
         <v>44917</v>
       </c>
-      <c r="H6" s="92" t="s">
-        <v>189</v>
-      </c>
-      <c r="I6" s="55" t="s">
-        <v>112</v>
-      </c>
-      <c r="J6" s="80" t="str">
+      <c r="H6" s="89" t="s">
+        <v>183</v>
+      </c>
+      <c r="I6" s="52" t="s">
+        <v>109</v>
+      </c>
+      <c r="J6" s="77" t="str">
         <f>_xlfn.CONCAT(B6,"-",D6,"-",TEXT(E6,"hh:mm"),"-",TEXT(F6,"hh:mm"),"-",TEXT(G6,"dd/mm/yyyy"),"-",TEXT(H6,"dd/mm/yyyy"))</f>
         <v>Carlos--Arbeladez--+57-3214533321-Jueves-13:00-19:00-22/12/2022-1/01/1000</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="26">
+      <c r="A7" s="24">
         <v>4</v>
       </c>
-      <c r="B7" s="91" t="str">
+      <c r="B7" s="88" t="str">
         <f>'M-Barbero'!K7</f>
         <v>Andres--Ramirez-Patiño-+91-9876543210</v>
       </c>
-      <c r="C7" s="91"/>
-      <c r="D7" s="26" t="s">
-        <v>194</v>
-      </c>
-      <c r="E7" s="55">
+      <c r="C7" s="88"/>
+      <c r="D7" s="24" t="s">
+        <v>188</v>
+      </c>
+      <c r="E7" s="52">
         <v>0.33333333333333298</v>
       </c>
-      <c r="F7" s="55">
+      <c r="F7" s="52">
         <v>0.58333333333333304</v>
       </c>
-      <c r="G7" s="93">
+      <c r="G7" s="90">
         <v>45915</v>
       </c>
-      <c r="H7" s="56">
+      <c r="H7" s="53">
         <v>46023</v>
       </c>
-      <c r="I7" s="94" t="s">
-        <v>127</v>
-      </c>
-      <c r="J7" s="80" t="str">
+      <c r="I7" s="91" t="s">
+        <v>124</v>
+      </c>
+      <c r="J7" s="77" t="str">
         <f>_xlfn.CONCAT(B7,"-",D7,"-",TEXT(E7,"hh:mm"),"-",TEXT(F7,"hh:mm"),"-",TEXT(G7,"dd/mm/yyyy"),"-",TEXT(H7,"dd/mm/yyyy"))</f>
         <v>Andres--Ramirez-Patiño-+91-9876543210-Sábado-08:00-14:00-15/09/2025-01/01/2026</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="26">
+      <c r="A8" s="24">
         <v>5</v>
       </c>
-      <c r="B8" s="91" t="str">
+      <c r="B8" s="88" t="str">
         <f>'M-Barbero'!K7</f>
         <v>Andres--Ramirez-Patiño-+91-9876543210</v>
       </c>
-      <c r="C8" s="91"/>
-      <c r="D8" s="26" t="s">
-        <v>195</v>
-      </c>
-      <c r="E8" s="55">
+      <c r="C8" s="88"/>
+      <c r="D8" s="24" t="s">
+        <v>189</v>
+      </c>
+      <c r="E8" s="52">
         <v>0.5</v>
       </c>
-      <c r="F8" s="55">
+      <c r="F8" s="52">
         <v>0.625</v>
       </c>
-      <c r="G8" s="93">
+      <c r="G8" s="90">
         <v>46054</v>
       </c>
-      <c r="H8" s="56">
+      <c r="H8" s="53">
         <v>46083</v>
       </c>
-      <c r="I8" s="94" t="s">
-        <v>127</v>
-      </c>
-      <c r="J8" s="80" t="str">
+      <c r="I8" s="91" t="s">
+        <v>124</v>
+      </c>
+      <c r="J8" s="77" t="str">
         <f>_xlfn.CONCAT(B8,"-",D8,"-",TEXT(E8,"hh:mm"),"-",TEXT(F8,"hh:mm"),"-",TEXT(G8,"dd/mm/yyyy"),"-",TEXT(H8,"dd/mm/yyyy"))</f>
         <v>Andres--Ramirez-Patiño-+91-9876543210-Festivo-12:00-15:00-01/02/2026-02/03/2026</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="H10" s="58"/>
+      <c r="H10" s="55"/>
     </row>
     <row r="14" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="28"/>
-      <c r="B14" s="29" t="s">
+      <c r="A14" s="26"/>
+      <c r="B14" s="27" t="s">
         <v>77</v>
       </c>
-      <c r="C14" s="29"/>
+      <c r="C14" s="27"/>
     </row>
     <row r="15" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="30"/>
-      <c r="B15" s="29" t="s">
+      <c r="A15" s="28"/>
+      <c r="B15" s="27" t="s">
         <v>78</v>
       </c>
-      <c r="C15" s="29"/>
+      <c r="C15" s="27"/>
     </row>
     <row r="16" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="59"/>
-      <c r="B16" s="29" t="s">
-        <v>196</v>
-      </c>
-      <c r="C16" s="29"/>
+      <c r="A16" s="56"/>
+      <c r="B16" s="27" t="s">
+        <v>190</v>
+      </c>
+      <c r="C16" s="27"/>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="31"/>
-      <c r="B17" s="29" t="s">
+      <c r="A17" s="29"/>
+      <c r="B17" s="27" t="s">
         <v>79</v>
       </c>
-      <c r="C17" s="29"/>
+      <c r="C17" s="27"/>
     </row>
     <row r="18" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="60"/>
-      <c r="B18" s="29" t="s">
-        <v>197</v>
-      </c>
-      <c r="C18" s="29"/>
+      <c r="A18" s="57"/>
+      <c r="B18" s="27" t="s">
+        <v>191</v>
+      </c>
+      <c r="C18" s="27"/>
     </row>
     <row r="19" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="44"/>
-      <c r="B19" s="29" t="s">
-        <v>134</v>
-      </c>
-      <c r="C19" s="29"/>
+      <c r="A19" s="42"/>
+      <c r="B19" s="27" t="s">
+        <v>131</v>
+      </c>
+      <c r="C19" s="27"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -9215,10 +9160,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="32" t="s">
+      <c r="B1" s="30" t="s">
         <v>33</v>
       </c>
     </row>
@@ -9360,7 +9305,7 @@
       <c r="K4" s="13"/>
       <c r="L4" s="13"/>
       <c r="M4" s="14" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="N4" s="13" t="s">
         <v>57</v>
@@ -9396,7 +9341,7 @@
         <v>57</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="E5" s="13" t="s">
         <v>57</v>
@@ -9408,10 +9353,10 @@
       <c r="J5" s="13"/>
       <c r="K5" s="13"/>
       <c r="L5" s="13" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="M5" s="14" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="N5" s="13" t="s">
         <v>57</v>
@@ -9430,7 +9375,7 @@
         <v>57</v>
       </c>
       <c r="T5" s="13" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="U5" s="13" t="s">
         <v>57</v>
@@ -9449,7 +9394,7 @@
         <v>57</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="E6" s="13" t="s">
         <v>55</v>
@@ -9461,10 +9406,10 @@
       <c r="J6" s="13"/>
       <c r="K6" s="13"/>
       <c r="L6" s="13" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="M6" s="14" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="N6" s="13" t="s">
         <v>57</v>
@@ -9565,10 +9510,10 @@
       </c>
       <c r="K8" s="13"/>
       <c r="L8" s="13" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="M8" s="14" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="N8" s="13" t="s">
         <v>55</v>
@@ -9604,7 +9549,7 @@
         <v>57</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="E9" s="13" t="s">
         <v>55</v>
@@ -9616,10 +9561,10 @@
       <c r="J9" s="13"/>
       <c r="K9" s="13"/>
       <c r="L9" s="13" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="M9" s="14" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="N9" s="13" t="s">
         <v>55</v>
@@ -9655,7 +9600,7 @@
         <v>57</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="E10" s="13" t="s">
         <v>55</v>
@@ -9667,10 +9612,10 @@
       <c r="J10" s="13"/>
       <c r="K10" s="13"/>
       <c r="L10" s="13" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="M10" s="14" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="N10" s="13" t="s">
         <v>55</v>
@@ -9689,7 +9634,7 @@
         <v>57</v>
       </c>
       <c r="T10" s="13" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="U10" s="13" t="s">
         <v>57</v>
@@ -9708,7 +9653,7 @@
         <v>57</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E11" s="13" t="s">
         <v>55</v>
@@ -9721,7 +9666,7 @@
       <c r="K11" s="13"/>
       <c r="L11" s="13"/>
       <c r="M11" s="14" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="N11" s="13" t="s">
         <v>57</v>
@@ -9740,7 +9685,7 @@
         <v>57</v>
       </c>
       <c r="T11" s="13" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="U11" s="13" t="s">
         <v>57</v>
@@ -9779,35 +9724,35 @@
       <c r="C13" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="D13" s="33"/>
-      <c r="E13" s="33"/>
-      <c r="F13" s="33"/>
-      <c r="G13" s="33"/>
-      <c r="H13" s="33"/>
-      <c r="I13" s="33"/>
-      <c r="J13" s="33"/>
-      <c r="K13" s="33"/>
-      <c r="L13" s="33"/>
-      <c r="M13" s="33"/>
-      <c r="N13" s="33"/>
-      <c r="O13" s="33"/>
-      <c r="P13" s="33"/>
-      <c r="Q13" s="33"/>
-      <c r="R13" s="33"/>
-      <c r="S13" s="33"/>
-      <c r="T13" s="33"/>
-      <c r="U13" s="33"/>
+      <c r="D13" s="31"/>
+      <c r="E13" s="31"/>
+      <c r="F13" s="31"/>
+      <c r="G13" s="31"/>
+      <c r="H13" s="31"/>
+      <c r="I13" s="31"/>
+      <c r="J13" s="31"/>
+      <c r="K13" s="31"/>
+      <c r="L13" s="31"/>
+      <c r="M13" s="31"/>
+      <c r="N13" s="31"/>
+      <c r="O13" s="31"/>
+      <c r="P13" s="31"/>
+      <c r="Q13" s="31"/>
+      <c r="R13" s="31"/>
+      <c r="S13" s="31"/>
+      <c r="T13" s="31"/>
+      <c r="U13" s="31"/>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A14" s="134" t="str">
+      <c r="A14" s="131" t="str">
         <f>'M-Descanso'!J3</f>
         <v>Combinación única</v>
       </c>
-      <c r="B14" s="135" t="str">
+      <c r="B14" s="132" t="str">
         <f>'M-Descanso'!J2</f>
         <v>Combinación única que indica que un mismo horario no puede tener dos mismas horas en la que empieze y termine</v>
       </c>
-      <c r="C14" s="34" t="str">
+      <c r="C14" s="32" t="str">
         <f>A4</f>
         <v>horario del barbero</v>
       </c>
@@ -9831,9 +9776,9 @@
       <c r="U14" s="4"/>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A15" s="134"/>
-      <c r="B15" s="134"/>
-      <c r="C15" s="34" t="str">
+      <c r="A15" s="131"/>
+      <c r="B15" s="131"/>
+      <c r="C15" s="32" t="str">
         <f>A5</f>
         <v>horaInicio</v>
       </c>
@@ -9857,9 +9802,9 @@
       <c r="U15" s="4"/>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A16" s="134"/>
-      <c r="B16" s="134"/>
-      <c r="C16" s="34" t="str">
+      <c r="A16" s="131"/>
+      <c r="B16" s="131"/>
+      <c r="C16" s="32" t="str">
         <f>A6</f>
         <v>horaFinal</v>
       </c>
@@ -9922,256 +9867,256 @@
       <c r="I1" s="5"/>
     </row>
     <row r="2" spans="1:10" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="45" t="s">
+      <c r="A2" s="43" t="s">
         <v>66</v>
       </c>
-      <c r="B2" s="46" t="s">
+      <c r="B2" s="44" t="s">
+        <v>257</v>
+      </c>
+      <c r="C2" s="44" t="s">
+        <v>258</v>
+      </c>
+      <c r="D2" s="44" t="s">
+        <v>259</v>
+      </c>
+      <c r="E2" s="44" t="s">
+        <v>260</v>
+      </c>
+      <c r="F2" s="65" t="s">
+        <v>261</v>
+      </c>
+      <c r="G2" s="43" t="s">
+        <v>262</v>
+      </c>
+      <c r="H2" s="43" t="s">
         <v>263</v>
       </c>
-      <c r="C2" s="46" t="s">
+      <c r="I2" s="43" t="s">
         <v>264</v>
       </c>
-      <c r="D2" s="46" t="s">
+      <c r="J2" s="44" t="s">
         <v>265</v>
       </c>
-      <c r="E2" s="46" t="s">
-        <v>266</v>
-      </c>
-      <c r="F2" s="68" t="s">
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="B3" s="46" t="s">
+        <v>326</v>
+      </c>
+      <c r="C3" s="49" t="s">
+        <v>251</v>
+      </c>
+      <c r="D3" s="49" t="s">
+        <v>252</v>
+      </c>
+      <c r="E3" s="22" t="s">
+        <v>73</v>
+      </c>
+      <c r="F3" s="86" t="s">
         <v>267</v>
       </c>
-      <c r="G2" s="45" t="s">
-        <v>268</v>
-      </c>
-      <c r="H2" s="45" t="s">
-        <v>269</v>
-      </c>
-      <c r="I2" s="45" t="s">
-        <v>270</v>
-      </c>
-      <c r="J2" s="46" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A3" s="23" t="s">
-        <v>70</v>
-      </c>
-      <c r="B3" s="48" t="s">
-        <v>332</v>
-      </c>
-      <c r="C3" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="D3" s="51" t="s">
-        <v>258</v>
-      </c>
-      <c r="E3" s="24" t="s">
-        <v>73</v>
-      </c>
-      <c r="F3" s="89" t="s">
-        <v>273</v>
-      </c>
-      <c r="G3" s="89" t="s">
-        <v>186</v>
-      </c>
-      <c r="H3" s="89" t="s">
-        <v>187</v>
-      </c>
-      <c r="I3" s="90" t="s">
-        <v>103</v>
-      </c>
-      <c r="J3" s="74" t="s">
-        <v>149</v>
+      <c r="G3" s="86" t="s">
+        <v>180</v>
+      </c>
+      <c r="H3" s="86" t="s">
+        <v>181</v>
+      </c>
+      <c r="I3" s="87" t="s">
+        <v>100</v>
+      </c>
+      <c r="J3" s="71" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="26">
+      <c r="A4" s="24">
         <v>1</v>
       </c>
-      <c r="B4" s="95" t="str">
+      <c r="B4" s="92" t="str">
         <f>'M-HorarioBarbero'!J4</f>
         <v>Juan-Fernando-García-Lopez-+57-3245627890-Lunes-10:00-16:00-03/05/2025-1/01/1000</v>
       </c>
-      <c r="C4" s="55">
+      <c r="C4" s="52">
         <v>0.5</v>
       </c>
-      <c r="D4" s="55">
+      <c r="D4" s="52">
         <v>0.58333333333333304</v>
       </c>
-      <c r="E4" s="54" t="s">
-        <v>274</v>
-      </c>
-      <c r="F4" s="41">
+      <c r="E4" s="51" t="s">
+        <v>268</v>
+      </c>
+      <c r="F4" s="39">
         <v>120</v>
       </c>
-      <c r="G4" s="56">
+      <c r="G4" s="53">
         <v>45780</v>
       </c>
-      <c r="H4" s="56" t="s">
-        <v>189</v>
-      </c>
-      <c r="I4" s="55" t="s">
-        <v>112</v>
-      </c>
-      <c r="J4" s="80" t="str">
+      <c r="H4" s="53" t="s">
+        <v>183</v>
+      </c>
+      <c r="I4" s="52" t="s">
+        <v>109</v>
+      </c>
+      <c r="J4" s="77" t="str">
         <f>_xlfn.CONCAT(B4,"-",TEXT(C4,"hh:mm"),"-",TEXT(D4,"hh:mm"))</f>
         <v>Juan-Fernando-García-Lopez-+57-3245627890-Lunes-10:00-16:00-03/05/2025-1/01/1000-12:00-14:00</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="26">
+      <c r="A5" s="24">
         <v>2</v>
       </c>
-      <c r="B5" s="95" t="str">
+      <c r="B5" s="92" t="str">
         <f>'M-HorarioBarbero'!J7</f>
         <v>Andres--Ramirez-Patiño-+91-9876543210-Sábado-08:00-14:00-15/09/2025-01/01/2026</v>
       </c>
-      <c r="C5" s="55">
+      <c r="C5" s="52">
         <v>0.52083333333333304</v>
       </c>
-      <c r="D5" s="96">
+      <c r="D5" s="93">
         <v>0.54166666666666696</v>
       </c>
-      <c r="E5" s="80" t="s">
-        <v>275</v>
-      </c>
-      <c r="F5" s="26">
+      <c r="E5" s="77" t="s">
+        <v>269</v>
+      </c>
+      <c r="F5" s="24">
         <v>30</v>
       </c>
-      <c r="G5" s="56">
+      <c r="G5" s="53">
         <v>45915</v>
       </c>
-      <c r="H5" s="56">
+      <c r="H5" s="53">
         <v>46023</v>
       </c>
-      <c r="I5" s="55" t="s">
-        <v>127</v>
-      </c>
-      <c r="J5" s="80" t="str">
+      <c r="I5" s="52" t="s">
+        <v>124</v>
+      </c>
+      <c r="J5" s="77" t="str">
         <f>_xlfn.CONCAT(B5,"-",TEXT(C5,"hh:mm"),"-",TEXT(D5,"hh:mm"))</f>
         <v>Andres--Ramirez-Patiño-+91-9876543210-Sábado-08:00-14:00-15/09/2025-01/01/2026-12:30-13:00</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="26">
+      <c r="A6" s="24">
         <v>3</v>
       </c>
-      <c r="B6" s="95" t="str">
+      <c r="B6" s="92" t="str">
         <f>'M-HorarioBarbero'!J6</f>
         <v>Carlos--Arbeladez--+57-3214533321-Jueves-13:00-19:00-22/12/2022-1/01/1000</v>
       </c>
-      <c r="C6" s="55">
+      <c r="C6" s="52">
         <v>0.58333333333333304</v>
       </c>
-      <c r="D6" s="55">
+      <c r="D6" s="52">
         <v>0.60416666666666696</v>
       </c>
-      <c r="E6" s="26" t="s">
-        <v>276</v>
-      </c>
-      <c r="F6" s="26">
+      <c r="E6" s="24" t="s">
+        <v>270</v>
+      </c>
+      <c r="F6" s="24">
         <v>30</v>
       </c>
-      <c r="G6" s="56">
+      <c r="G6" s="53">
         <v>44917</v>
       </c>
-      <c r="H6" s="92" t="s">
-        <v>189</v>
-      </c>
-      <c r="I6" s="55" t="s">
-        <v>112</v>
-      </c>
-      <c r="J6" s="80" t="str">
+      <c r="H6" s="89" t="s">
+        <v>183</v>
+      </c>
+      <c r="I6" s="52" t="s">
+        <v>109</v>
+      </c>
+      <c r="J6" s="77" t="str">
         <f>_xlfn.CONCAT(B6,"-",TEXT(C6,"hh:mm"),"-",TEXT(D6,"hh:mm"))</f>
         <v>Carlos--Arbeladez--+57-3214533321-Jueves-13:00-19:00-22/12/2022-1/01/1000-14:00-14:30</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="26">
+      <c r="A7" s="24">
         <v>4</v>
       </c>
-      <c r="B7" s="95" t="str">
+      <c r="B7" s="92" t="str">
         <f>'M-HorarioBarbero'!J5</f>
         <v>Juan-David-Ortiz-Sanchez-+57-3124518923-Martes-09:00-15:00-02/03/2025-1/01/1000</v>
       </c>
-      <c r="C7" s="55">
+      <c r="C7" s="52">
         <v>0.47916666666666702</v>
       </c>
-      <c r="D7" s="55">
+      <c r="D7" s="52">
         <v>0.54166666666666696</v>
       </c>
-      <c r="E7" s="26" t="s">
-        <v>277</v>
-      </c>
-      <c r="F7" s="26">
+      <c r="E7" s="24" t="s">
+        <v>271</v>
+      </c>
+      <c r="F7" s="24">
         <v>90</v>
       </c>
-      <c r="G7" s="97">
+      <c r="G7" s="94">
         <v>45718</v>
       </c>
-      <c r="H7" s="92" t="s">
-        <v>189</v>
-      </c>
-      <c r="I7" s="98" t="s">
-        <v>112</v>
-      </c>
-      <c r="J7" s="80" t="str">
+      <c r="H7" s="89" t="s">
+        <v>183</v>
+      </c>
+      <c r="I7" s="95" t="s">
+        <v>109</v>
+      </c>
+      <c r="J7" s="77" t="str">
         <f>_xlfn.CONCAT(B7,"-",TEXT(C7,"hh:mm"),"-",TEXT(D7,"hh:mm"))</f>
         <v>Juan-David-Ortiz-Sanchez-+57-3124518923-Martes-09:00-15:00-02/03/2025-1/01/1000-11:30-13:00</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="G8" s="99"/>
-      <c r="H8" s="99"/>
-      <c r="I8" s="100"/>
+      <c r="G8" s="96"/>
+      <c r="H8" s="96"/>
+      <c r="I8" s="97"/>
     </row>
     <row r="13" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="28"/>
-      <c r="B13" s="29" t="s">
+      <c r="A13" s="26"/>
+      <c r="B13" s="27" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="30"/>
-      <c r="B14" s="29" t="s">
+      <c r="A14" s="28"/>
+      <c r="B14" s="27" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="59"/>
-      <c r="B15" s="29" t="s">
-        <v>196</v>
+      <c r="A15" s="56"/>
+      <c r="B15" s="27" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="31"/>
-      <c r="B16" s="29" t="s">
+      <c r="A16" s="29"/>
+      <c r="B16" s="27" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="60"/>
-      <c r="B17" s="29" t="s">
-        <v>197</v>
+      <c r="A17" s="57"/>
+      <c r="B17" s="27" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="43"/>
-      <c r="B18" s="29" t="s">
-        <v>133</v>
+      <c r="A18" s="41"/>
+      <c r="B18" s="27" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="61"/>
-      <c r="B19" s="29" t="s">
-        <v>198</v>
+      <c r="A19" s="58"/>
+      <c r="B19" s="27" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="44"/>
-      <c r="B20" s="29" t="s">
-        <v>134</v>
+      <c r="A20" s="42"/>
+      <c r="B20" s="27" t="s">
+        <v>131</v>
       </c>
     </row>
   </sheetData>
@@ -10217,10 +10162,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="32" t="s">
+      <c r="B1" s="30" t="s">
         <v>33</v>
       </c>
     </row>
@@ -10363,7 +10308,7 @@
       <c r="K4" s="13"/>
       <c r="L4" s="13"/>
       <c r="M4" s="14" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="N4" s="13" t="s">
         <v>57</v>
@@ -10399,7 +10344,7 @@
         <v>57</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="E5" s="13" t="s">
         <v>55</v>
@@ -10411,10 +10356,10 @@
       <c r="J5" s="13"/>
       <c r="K5" s="13"/>
       <c r="L5" s="13" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="M5" s="14" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="N5" s="13" t="s">
         <v>57</v>
@@ -10450,7 +10395,7 @@
         <v>57</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="E6" s="13" t="s">
         <v>55</v>
@@ -10462,10 +10407,10 @@
       <c r="J6" s="13"/>
       <c r="K6" s="13"/>
       <c r="L6" s="13" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="M6" s="14" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="N6" s="13" t="s">
         <v>57</v>
@@ -10566,10 +10511,10 @@
       </c>
       <c r="K8" s="13"/>
       <c r="L8" s="13" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="M8" s="14" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="N8" s="13" t="s">
         <v>55</v>
@@ -10625,35 +10570,35 @@
       <c r="C10" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="D10" s="33"/>
-      <c r="E10" s="33"/>
-      <c r="F10" s="33"/>
-      <c r="G10" s="33"/>
-      <c r="H10" s="33"/>
-      <c r="I10" s="33"/>
-      <c r="J10" s="33"/>
-      <c r="K10" s="33"/>
-      <c r="L10" s="33"/>
-      <c r="M10" s="33"/>
-      <c r="N10" s="33"/>
-      <c r="O10" s="33"/>
-      <c r="P10" s="33"/>
-      <c r="Q10" s="33"/>
-      <c r="R10" s="33"/>
-      <c r="S10" s="33"/>
-      <c r="T10" s="33"/>
-      <c r="U10" s="33"/>
+      <c r="D10" s="31"/>
+      <c r="E10" s="31"/>
+      <c r="F10" s="31"/>
+      <c r="G10" s="31"/>
+      <c r="H10" s="31"/>
+      <c r="I10" s="31"/>
+      <c r="J10" s="31"/>
+      <c r="K10" s="31"/>
+      <c r="L10" s="31"/>
+      <c r="M10" s="31"/>
+      <c r="N10" s="31"/>
+      <c r="O10" s="31"/>
+      <c r="P10" s="31"/>
+      <c r="Q10" s="31"/>
+      <c r="R10" s="31"/>
+      <c r="S10" s="31"/>
+      <c r="T10" s="31"/>
+      <c r="U10" s="31"/>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A11" s="134" t="str">
+      <c r="A11" s="131" t="str">
         <f>'M-Bloqueo'!G3</f>
         <v>Combinación única</v>
       </c>
-      <c r="B11" s="135" t="str">
+      <c r="B11" s="132" t="str">
         <f>'M-Bloqueo'!G2</f>
         <v>Combinación única que indica que una misma agenda no puede tener dos bloqueos en una misma fecha, horaInicio y horaFinal</v>
       </c>
-      <c r="C11" s="34" t="str">
+      <c r="C11" s="32" t="str">
         <f>A4</f>
         <v>agenda</v>
       </c>
@@ -10677,9 +10622,9 @@
       <c r="U11" s="4"/>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A12" s="134"/>
-      <c r="B12" s="134"/>
-      <c r="C12" s="34" t="str">
+      <c r="A12" s="131"/>
+      <c r="B12" s="131"/>
+      <c r="C12" s="32" t="str">
         <f>A5</f>
         <v>fechaHoraInicio</v>
       </c>
@@ -10703,9 +10648,9 @@
       <c r="U12" s="4"/>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A13" s="134"/>
-      <c r="B13" s="134"/>
-      <c r="C13" s="34" t="str">
+      <c r="A13" s="131"/>
+      <c r="B13" s="131"/>
+      <c r="C13" s="32" t="str">
         <f>A6</f>
         <v>fechaHoraFinal</v>
       </c>
@@ -10767,191 +10712,191 @@
       <c r="D1" s="5"/>
     </row>
     <row r="2" spans="1:7" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="45" t="s">
+      <c r="A2" s="43" t="s">
         <v>66</v>
       </c>
-      <c r="B2" s="46" t="s">
+      <c r="B2" s="44" t="s">
+        <v>277</v>
+      </c>
+      <c r="C2" s="65" t="s">
+        <v>278</v>
+      </c>
+      <c r="D2" s="65" t="s">
+        <v>279</v>
+      </c>
+      <c r="E2" s="44" t="s">
+        <v>280</v>
+      </c>
+      <c r="F2" s="44" t="s">
+        <v>281</v>
+      </c>
+      <c r="G2" s="44" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="B3" s="83" t="s">
+        <v>266</v>
+      </c>
+      <c r="C3" s="98" t="s">
         <v>283</v>
       </c>
-      <c r="C2" s="68" t="s">
+      <c r="D3" s="98" t="s">
         <v>284</v>
       </c>
-      <c r="D2" s="68" t="s">
-        <v>285</v>
-      </c>
-      <c r="E2" s="46" t="s">
-        <v>286</v>
-      </c>
-      <c r="F2" s="46" t="s">
-        <v>287</v>
-      </c>
-      <c r="G2" s="46" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="23" t="s">
-        <v>70</v>
-      </c>
-      <c r="B3" s="86" t="s">
-        <v>272</v>
-      </c>
-      <c r="C3" s="101" t="s">
-        <v>289</v>
-      </c>
-      <c r="D3" s="101" t="s">
-        <v>290</v>
-      </c>
-      <c r="E3" s="87" t="s">
+      <c r="E3" s="84" t="s">
         <v>73</v>
       </c>
-      <c r="F3" s="38" t="s">
-        <v>273</v>
-      </c>
-      <c r="G3" s="74" t="s">
-        <v>149</v>
+      <c r="F3" s="36" t="s">
+        <v>267</v>
+      </c>
+      <c r="G3" s="71" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="26">
+      <c r="A4" s="24">
         <v>1</v>
       </c>
-      <c r="B4" s="95" t="str">
+      <c r="B4" s="92" t="str">
         <f>'M-HorarioBarbero'!J4</f>
         <v>Juan-Fernando-García-Lopez-+57-3245627890-Lunes-10:00-16:00-03/05/2025-1/01/1000</v>
       </c>
-      <c r="C4" s="102">
+      <c r="C4" s="99">
         <v>46272.416666666701</v>
       </c>
-      <c r="D4" s="102">
+      <c r="D4" s="99">
         <v>46272.5</v>
       </c>
-      <c r="E4" s="103" t="s">
-        <v>291</v>
-      </c>
-      <c r="F4" s="26">
+      <c r="E4" s="100" t="s">
+        <v>285</v>
+      </c>
+      <c r="F4" s="24">
         <v>120</v>
       </c>
-      <c r="G4" s="80" t="str">
+      <c r="G4" s="77" t="str">
         <f>_xlfn.CONCAT(B4,"-",TEXT(C4,"dd/mm/yyyy hh:mm"),"-",TEXT(D4,"dd/mm/yyyy hh:mm"))</f>
         <v>Juan-Fernando-García-Lopez-+57-3245627890-Lunes-10:00-16:00-03/05/2025-1/01/1000-07/09/2026 10:00-07/09/2026 12:00</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="26">
+      <c r="A5" s="24">
         <v>2</v>
       </c>
-      <c r="B5" s="95" t="str">
+      <c r="B5" s="92" t="str">
         <f>'M-HorarioBarbero'!J5</f>
         <v>Juan-David-Ortiz-Sanchez-+57-3124518923-Martes-09:00-15:00-02/03/2025-1/01/1000</v>
       </c>
-      <c r="C5" s="102">
+      <c r="C5" s="99">
         <v>46273.395833333299</v>
       </c>
-      <c r="D5" s="102">
+      <c r="D5" s="99">
         <v>46273.458333333299</v>
       </c>
-      <c r="E5" s="104" t="s">
-        <v>292</v>
-      </c>
-      <c r="F5" s="26">
+      <c r="E5" s="101" t="s">
+        <v>286</v>
+      </c>
+      <c r="F5" s="24">
         <v>90</v>
       </c>
-      <c r="G5" s="80" t="str">
+      <c r="G5" s="77" t="str">
         <f>_xlfn.CONCAT(B5,"-",TEXT(C5,"dd/mm/yyyy hh:mm"),"-",TEXT(D5,"dd/mm/yyyy hh:mm"))</f>
         <v>Juan-David-Ortiz-Sanchez-+57-3124518923-Martes-09:00-15:00-02/03/2025-1/01/1000-08/09/2026 09:30-08/09/2026 11:00</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="26">
+      <c r="A6" s="24">
         <v>3</v>
       </c>
-      <c r="B6" s="95" t="str">
+      <c r="B6" s="92" t="str">
         <f>'M-HorarioBarbero'!J6</f>
         <v>Carlos--Arbeladez--+57-3214533321-Jueves-13:00-19:00-22/12/2022-1/01/1000</v>
       </c>
-      <c r="C6" s="102">
+      <c r="C6" s="99">
         <v>46275.541666666701</v>
       </c>
-      <c r="D6" s="102">
+      <c r="D6" s="99">
         <v>46275.583333333299</v>
       </c>
-      <c r="E6" s="104" t="s">
-        <v>293</v>
-      </c>
-      <c r="F6" s="26">
+      <c r="E6" s="101" t="s">
+        <v>287</v>
+      </c>
+      <c r="F6" s="24">
         <v>60</v>
       </c>
-      <c r="G6" s="80" t="str">
+      <c r="G6" s="77" t="str">
         <f>_xlfn.CONCAT(B6,"-",TEXT(C6,"dd/mm/yyyy hh:mm"),"-",TEXT(D6,"dd/mm/yyyy hh:mm"))</f>
         <v>Carlos--Arbeladez--+57-3214533321-Jueves-13:00-19:00-22/12/2022-1/01/1000-10/09/2026 13:00-10/09/2026 14:00</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="26">
+      <c r="A7" s="24">
         <v>4</v>
       </c>
-      <c r="B7" s="95" t="str">
+      <c r="B7" s="92" t="str">
         <f>'M-HorarioBarbero'!J5</f>
         <v>Juan-David-Ortiz-Sanchez-+57-3124518923-Martes-09:00-15:00-02/03/2025-1/01/1000</v>
       </c>
-      <c r="C7" s="102">
+      <c r="C7" s="99">
         <v>46301.541666666701</v>
       </c>
-      <c r="D7" s="102">
+      <c r="D7" s="99">
         <v>46301.625</v>
       </c>
-      <c r="E7" s="104" t="s">
-        <v>294</v>
-      </c>
-      <c r="F7" s="26">
+      <c r="E7" s="101" t="s">
+        <v>288</v>
+      </c>
+      <c r="F7" s="24">
         <v>120</v>
       </c>
-      <c r="G7" s="80" t="str">
+      <c r="G7" s="77" t="str">
         <f>_xlfn.CONCAT(B7,"-",TEXT(C7,"dd/mm/yyyy hh:mm"),"-",TEXT(D7,"dd/mm/yyyy hh:mm"))</f>
         <v>Juan-David-Ortiz-Sanchez-+57-3124518923-Martes-09:00-15:00-02/03/2025-1/01/1000-06/10/2026 13:00-06/10/2026 15:00</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="28"/>
-      <c r="B13" s="29" t="s">
+      <c r="A13" s="26"/>
+      <c r="B13" s="27" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="30"/>
-      <c r="B14" s="29" t="s">
+      <c r="A14" s="28"/>
+      <c r="B14" s="27" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="59"/>
-      <c r="B15" s="29" t="s">
-        <v>196</v>
+      <c r="A15" s="56"/>
+      <c r="B15" s="27" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="31"/>
-      <c r="B16" s="29" t="s">
+      <c r="A16" s="29"/>
+      <c r="B16" s="27" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="105"/>
-      <c r="B17" s="29" t="s">
-        <v>295</v>
+      <c r="A17" s="102"/>
+      <c r="B17" s="27" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="43"/>
-      <c r="B18" s="29" t="s">
-        <v>133</v>
+      <c r="A18" s="41"/>
+      <c r="B18" s="27" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19" s="44"/>
-      <c r="B19" s="29" t="s">
-        <v>134</v>
+      <c r="A19" s="42"/>
+      <c r="B19" s="27" t="s">
+        <v>131</v>
       </c>
     </row>
   </sheetData>
@@ -10997,10 +10942,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="32" t="s">
+      <c r="B1" s="30" t="s">
         <v>33</v>
       </c>
     </row>
@@ -11142,7 +11087,7 @@
       <c r="K4" s="13"/>
       <c r="L4" s="13"/>
       <c r="M4" s="14" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="N4" s="13" t="s">
         <v>57</v>
@@ -11191,7 +11136,7 @@
       <c r="K5" s="13"/>
       <c r="L5" s="13"/>
       <c r="M5" s="14" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="N5" s="13" t="s">
         <v>57</v>
@@ -11227,7 +11172,7 @@
         <v>57</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="E6" s="13" t="s">
         <v>55</v>
@@ -11239,7 +11184,7 @@
       <c r="J6" s="13"/>
       <c r="K6" s="13"/>
       <c r="L6" s="13" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="M6" s="14"/>
       <c r="N6" s="13" t="s">
@@ -11276,7 +11221,7 @@
         <v>57</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="E7" s="13" t="s">
         <v>55</v>
@@ -11288,10 +11233,10 @@
       <c r="J7" s="13"/>
       <c r="K7" s="13"/>
       <c r="L7" s="13" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="M7" s="14" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="N7" s="13" t="s">
         <v>55</v>
@@ -11344,7 +11289,7 @@
       <c r="K8" s="13"/>
       <c r="L8" s="13"/>
       <c r="M8" s="14" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="N8" s="13" t="s">
         <v>57</v>
@@ -11363,7 +11308,7 @@
         <v>57</v>
       </c>
       <c r="T8" s="13" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="U8" s="13" t="s">
         <v>57</v>
@@ -11402,36 +11347,36 @@
       <c r="C10" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="D10" s="33"/>
-      <c r="E10" s="33"/>
-      <c r="F10" s="33"/>
-      <c r="G10" s="33"/>
-      <c r="H10" s="33"/>
-      <c r="I10" s="33"/>
-      <c r="J10" s="33"/>
-      <c r="K10" s="33"/>
-      <c r="L10" s="33"/>
-      <c r="M10" s="33"/>
-      <c r="N10" s="33"/>
-      <c r="O10" s="33"/>
-      <c r="P10" s="33"/>
-      <c r="Q10" s="33"/>
-      <c r="R10" s="33"/>
-      <c r="S10" s="33"/>
-      <c r="T10" s="33"/>
-      <c r="U10" s="33"/>
+      <c r="D10" s="31"/>
+      <c r="E10" s="31"/>
+      <c r="F10" s="31"/>
+      <c r="G10" s="31"/>
+      <c r="H10" s="31"/>
+      <c r="I10" s="31"/>
+      <c r="J10" s="31"/>
+      <c r="K10" s="31"/>
+      <c r="L10" s="31"/>
+      <c r="M10" s="31"/>
+      <c r="N10" s="31"/>
+      <c r="O10" s="31"/>
+      <c r="P10" s="31"/>
+      <c r="Q10" s="31"/>
+      <c r="R10" s="31"/>
+      <c r="S10" s="31"/>
+      <c r="T10" s="31"/>
+      <c r="U10" s="31"/>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A11" s="134" t="str">
+      <c r="A11" s="131" t="str">
         <f>'M-Cita'!G3</f>
         <v>Combinación única</v>
       </c>
-      <c r="B11" s="135" t="str">
+      <c r="B11" s="132" t="str">
         <f>'M-Cita'!G2</f>
         <v xml:space="preserve">
 Combinación única que indica que una cita no puede existir dentro de una agenda con la misma fecha y hora de inicio para la cita</v>
       </c>
-      <c r="C11" s="34" t="str">
+      <c r="C11" s="32" t="str">
         <f>A5</f>
         <v>agenda</v>
       </c>
@@ -11455,9 +11400,9 @@
       <c r="U11" s="4"/>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A12" s="134"/>
-      <c r="B12" s="134"/>
-      <c r="C12" s="34" t="str">
+      <c r="A12" s="131"/>
+      <c r="B12" s="131"/>
+      <c r="C12" s="32" t="str">
         <f>A6</f>
         <v>fechaHora</v>
       </c>
@@ -11509,345 +11454,345 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="106" t="s">
+      <c r="A1" s="103" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="106" t="s">
+      <c r="B1" s="103" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="58.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="107" t="s">
+      <c r="A2" s="104" t="s">
         <v>66</v>
       </c>
-      <c r="B2" s="107" t="s">
+      <c r="B2" s="104" t="s">
+        <v>293</v>
+      </c>
+      <c r="C2" s="105" t="s">
+        <v>294</v>
+      </c>
+      <c r="D2" s="105" t="s">
+        <v>295</v>
+      </c>
+      <c r="E2" s="105" t="s">
+        <v>296</v>
+      </c>
+      <c r="F2" s="105" t="s">
+        <v>297</v>
+      </c>
+      <c r="G2" s="105" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="106" t="s">
+        <v>70</v>
+      </c>
+      <c r="B3" s="46" t="s">
         <v>299</v>
       </c>
-      <c r="C2" s="108" t="s">
+      <c r="C3" s="46" t="s">
+        <v>266</v>
+      </c>
+      <c r="D3" s="107" t="s">
         <v>300</v>
       </c>
-      <c r="D2" s="108" t="s">
+      <c r="E3" s="108" t="s">
         <v>301</v>
       </c>
-      <c r="E2" s="108" t="s">
+      <c r="F3" s="109" t="s">
         <v>302</v>
       </c>
-      <c r="F2" s="108" t="s">
-        <v>303</v>
-      </c>
-      <c r="G2" s="108" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="109" t="s">
-        <v>70</v>
-      </c>
-      <c r="B3" s="48" t="s">
-        <v>305</v>
-      </c>
-      <c r="C3" s="48" t="s">
-        <v>272</v>
-      </c>
-      <c r="D3" s="110" t="s">
-        <v>306</v>
-      </c>
-      <c r="E3" s="111" t="s">
-        <v>307</v>
-      </c>
-      <c r="F3" s="112" t="s">
-        <v>308</v>
-      </c>
-      <c r="G3" s="113" t="s">
-        <v>149</v>
+      <c r="G3" s="110" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="26">
+      <c r="A4" s="24">
         <v>1</v>
       </c>
-      <c r="B4" s="114" t="str">
+      <c r="B4" s="111" t="str">
         <f>_xlfn.CONCAT('M-Cliente'!B4," ",'M-Cliente'!C4," ", 'M-Cliente'!D4," ",'M-Cliente'!E4)</f>
         <v xml:space="preserve">Juan  Gómez </v>
       </c>
-      <c r="C4" s="115" t="str">
+      <c r="C4" s="112" t="str">
         <f>'M-HorarioBarbero'!J4</f>
         <v>Juan-Fernando-García-Lopez-+57-3245627890-Lunes-10:00-16:00-03/05/2025-1/01/1000</v>
       </c>
-      <c r="D4" s="116">
+      <c r="D4" s="113">
         <v>46265.416666666701</v>
       </c>
-      <c r="E4" s="116">
+      <c r="E4" s="113">
         <v>46265.447916666701</v>
       </c>
-      <c r="F4" s="26" t="s">
-        <v>298</v>
-      </c>
-      <c r="G4" s="80" t="str">
+      <c r="F4" s="24" t="s">
+        <v>292</v>
+      </c>
+      <c r="G4" s="77" t="str">
         <f t="shared" ref="G4:G12" si="0">_xlfn.CONCAT(C4,"-",TEXT(D4,"dd/mm/yyyy/hh:mm"))</f>
         <v>Juan-Fernando-García-Lopez-+57-3245627890-Lunes-10:00-16:00-03/05/2025-1/01/1000-31/08/2026/10:00</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="26">
+      <c r="A5" s="24">
         <v>2</v>
       </c>
-      <c r="B5" s="114" t="str">
+      <c r="B5" s="111" t="str">
         <f>_xlfn.CONCAT('M-Cliente'!B5," ",'M-Cliente'!C5," ", 'M-Cliente'!D5," ",'M-Cliente'!E5)</f>
         <v>Jose Miguel Ramirez Perez</v>
       </c>
-      <c r="C5" s="115" t="str">
+      <c r="C5" s="112" t="str">
         <f>'M-HorarioBarbero'!J5</f>
         <v>Juan-David-Ortiz-Sanchez-+57-3124518923-Martes-09:00-15:00-02/03/2025-1/01/1000</v>
       </c>
-      <c r="D5" s="116">
+      <c r="D5" s="113">
         <v>46091.395833333299</v>
       </c>
-      <c r="E5" s="116">
+      <c r="E5" s="113">
         <v>46091.430555555598</v>
       </c>
-      <c r="F5" s="26" t="s">
-        <v>309</v>
-      </c>
-      <c r="G5" s="80" t="str">
+      <c r="F5" s="24" t="s">
+        <v>303</v>
+      </c>
+      <c r="G5" s="77" t="str">
         <f t="shared" si="0"/>
         <v>Juan-David-Ortiz-Sanchez-+57-3124518923-Martes-09:00-15:00-02/03/2025-1/01/1000-10/03/2026/09:30</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="26">
+      <c r="A6" s="24">
         <v>3</v>
       </c>
-      <c r="B6" s="114" t="str">
+      <c r="B6" s="111" t="str">
         <f>_xlfn.CONCAT('M-Cliente'!B6," ",'M-Cliente'!C6," ", 'M-Cliente'!D6," ",'M-Cliente'!E6)</f>
         <v>Simon  Ochoa Ramirez</v>
       </c>
-      <c r="C6" s="115" t="str">
+      <c r="C6" s="112" t="str">
         <f>'M-HorarioBarbero'!J6</f>
         <v>Carlos--Arbeladez--+57-3214533321-Jueves-13:00-19:00-22/12/2022-1/01/1000</v>
       </c>
-      <c r="D6" s="116">
+      <c r="D6" s="113">
         <v>46156.541666666701</v>
       </c>
-      <c r="E6" s="116">
+      <c r="E6" s="113">
         <v>46156.552083333299</v>
       </c>
-      <c r="F6" s="26" t="s">
-        <v>310</v>
-      </c>
-      <c r="G6" s="80" t="str">
+      <c r="F6" s="24" t="s">
+        <v>304</v>
+      </c>
+      <c r="G6" s="77" t="str">
         <f t="shared" si="0"/>
         <v>Carlos--Arbeladez--+57-3214533321-Jueves-13:00-19:00-22/12/2022-1/01/1000-14/05/2026/13:00</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="26">
+      <c r="A7" s="24">
         <v>4</v>
       </c>
-      <c r="B7" s="114" t="str">
+      <c r="B7" s="111" t="str">
         <f>_xlfn.CONCAT('M-Cliente'!B7," ",'M-Cliente'!C7," ", 'M-Cliente'!D7," ",'M-Cliente'!E7)</f>
         <v xml:space="preserve">Alexis  Gallego </v>
       </c>
-      <c r="C7" s="115" t="str">
+      <c r="C7" s="112" t="str">
         <f>'M-HorarioBarbero'!J7</f>
         <v>Andres--Ramirez-Patiño-+91-9876543210-Sábado-08:00-14:00-15/09/2025-01/01/2026</v>
       </c>
-      <c r="D7" s="116">
+      <c r="D7" s="113">
         <v>45983.541666666701</v>
       </c>
-      <c r="E7" s="116">
+      <c r="E7" s="113">
         <v>45983.569444444503</v>
       </c>
-      <c r="F7" s="26" t="s">
-        <v>311</v>
-      </c>
-      <c r="G7" s="80" t="str">
+      <c r="F7" s="24" t="s">
+        <v>305</v>
+      </c>
+      <c r="G7" s="77" t="str">
         <f t="shared" si="0"/>
         <v>Andres--Ramirez-Patiño-+91-9876543210-Sábado-08:00-14:00-15/09/2025-01/01/2026-22/11/2025/13:00</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="26">
+      <c r="A8" s="24">
         <v>5</v>
       </c>
-      <c r="B8" s="114" t="str">
+      <c r="B8" s="111" t="str">
         <f>_xlfn.CONCAT('M-Cliente'!B7," ",'M-Cliente'!C7," ", 'M-Cliente'!D7," ",'M-Cliente'!E7)</f>
         <v xml:space="preserve">Alexis  Gallego </v>
       </c>
-      <c r="C8" s="115" t="str">
+      <c r="C8" s="112" t="str">
         <f>'M-HorarioBarbero'!J6</f>
         <v>Carlos--Arbeladez--+57-3214533321-Jueves-13:00-19:00-22/12/2022-1/01/1000</v>
       </c>
-      <c r="D8" s="116">
+      <c r="D8" s="113">
         <v>46240.75</v>
       </c>
-      <c r="E8" s="116">
+      <c r="E8" s="113">
         <v>46240.760416666701</v>
       </c>
-      <c r="F8" s="26" t="s">
-        <v>312</v>
-      </c>
-      <c r="G8" s="80" t="str">
+      <c r="F8" s="24" t="s">
+        <v>306</v>
+      </c>
+      <c r="G8" s="77" t="str">
         <f t="shared" si="0"/>
         <v>Carlos--Arbeladez--+57-3214533321-Jueves-13:00-19:00-22/12/2022-1/01/1000-06/08/2026/18:00</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="26">
+      <c r="A9" s="24">
         <v>6</v>
       </c>
-      <c r="B9" s="114" t="str">
+      <c r="B9" s="111" t="str">
         <f>_xlfn.CONCAT('M-Cliente'!B4," ",'M-Cliente'!C4," ", 'M-Cliente'!D4," ",'M-Cliente'!E4)</f>
         <v xml:space="preserve">Juan  Gómez </v>
       </c>
-      <c r="C9" s="115" t="str">
+      <c r="C9" s="112" t="str">
         <f>'M-HorarioBarbero'!J5</f>
         <v>Juan-David-Ortiz-Sanchez-+57-3124518923-Martes-09:00-15:00-02/03/2025-1/01/1000</v>
       </c>
-      <c r="D9" s="116">
+      <c r="D9" s="113">
         <v>46266.583333333299</v>
       </c>
-      <c r="E9" s="116">
+      <c r="E9" s="113">
         <v>46266.590277777803</v>
       </c>
-      <c r="F9" s="26" t="s">
-        <v>298</v>
-      </c>
-      <c r="G9" s="80" t="str">
+      <c r="F9" s="24" t="s">
+        <v>292</v>
+      </c>
+      <c r="G9" s="77" t="str">
         <f t="shared" si="0"/>
         <v>Juan-David-Ortiz-Sanchez-+57-3124518923-Martes-09:00-15:00-02/03/2025-1/01/1000-01/09/2026/14:00</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="26">
+      <c r="A10" s="24">
         <v>7</v>
       </c>
-      <c r="B10" s="114" t="str">
+      <c r="B10" s="111" t="str">
         <f>_xlfn.CONCAT('M-Cliente'!B8," ",'M-Cliente'!C8," ", 'M-Cliente'!D8," ",'M-Cliente'!E8)</f>
         <v>Kevin Andrés Muñoz Salazar</v>
       </c>
-      <c r="C10" s="115" t="str">
+      <c r="C10" s="112" t="str">
         <f>'M-HorarioBarbero'!J4</f>
         <v>Juan-Fernando-García-Lopez-+57-3245627890-Lunes-10:00-16:00-03/05/2025-1/01/1000</v>
       </c>
-      <c r="D10" s="116">
+      <c r="D10" s="113">
         <v>46174.416666666701</v>
       </c>
-      <c r="E10" s="116">
+      <c r="E10" s="113">
         <v>46174.447916666701</v>
       </c>
-      <c r="F10" s="26" t="s">
-        <v>311</v>
-      </c>
-      <c r="G10" s="80" t="str">
+      <c r="F10" s="24" t="s">
+        <v>305</v>
+      </c>
+      <c r="G10" s="77" t="str">
         <f t="shared" si="0"/>
         <v>Juan-Fernando-García-Lopez-+57-3245627890-Lunes-10:00-16:00-03/05/2025-1/01/1000-01/06/2026/10:00</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="26">
+      <c r="A11" s="24">
         <v>8</v>
       </c>
-      <c r="B11" s="114" t="str">
+      <c r="B11" s="111" t="str">
         <f>_xlfn.CONCAT('M-Cliente'!B8," ",'M-Cliente'!C8," ", 'M-Cliente'!D8," ",'M-Cliente'!E8)</f>
         <v>Kevin Andrés Muñoz Salazar</v>
       </c>
-      <c r="C11" s="115" t="str">
+      <c r="C11" s="112" t="str">
         <f>'M-HorarioBarbero'!J5</f>
         <v>Juan-David-Ortiz-Sanchez-+57-3124518923-Martes-09:00-15:00-02/03/2025-1/01/1000</v>
       </c>
-      <c r="D11" s="116">
+      <c r="D11" s="113">
         <v>46189.375</v>
       </c>
-      <c r="E11" s="116">
+      <c r="E11" s="113">
         <v>46189.381944444503</v>
       </c>
-      <c r="F11" s="26" t="s">
-        <v>311</v>
-      </c>
-      <c r="G11" s="80" t="str">
+      <c r="F11" s="24" t="s">
+        <v>305</v>
+      </c>
+      <c r="G11" s="77" t="str">
         <f t="shared" si="0"/>
         <v>Juan-David-Ortiz-Sanchez-+57-3124518923-Martes-09:00-15:00-02/03/2025-1/01/1000-16/06/2026/09:00</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="26">
+      <c r="A12" s="24">
         <v>9</v>
       </c>
-      <c r="B12" s="114" t="str">
+      <c r="B12" s="111" t="str">
         <f>_xlfn.CONCAT('M-Cliente'!B8," ",'M-Cliente'!C8," ", 'M-Cliente'!D8," ",'M-Cliente'!E8)</f>
         <v>Kevin Andrés Muñoz Salazar</v>
       </c>
-      <c r="C12" s="115" t="str">
+      <c r="C12" s="112" t="str">
         <f>'M-HorarioBarbero'!J6</f>
         <v>Carlos--Arbeladez--+57-3214533321-Jueves-13:00-19:00-22/12/2022-1/01/1000</v>
       </c>
-      <c r="D12" s="116">
+      <c r="D12" s="113">
         <v>46205.625</v>
       </c>
-      <c r="E12" s="116">
+      <c r="E12" s="113">
         <v>46205.635416666701</v>
       </c>
-      <c r="F12" s="26" t="s">
-        <v>311</v>
-      </c>
-      <c r="G12" s="80" t="str">
+      <c r="F12" s="24" t="s">
+        <v>305</v>
+      </c>
+      <c r="G12" s="77" t="str">
         <f t="shared" si="0"/>
         <v>Carlos--Arbeladez--+57-3214533321-Jueves-13:00-19:00-22/12/2022-1/01/1000-02/07/2026/15:00</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="29"/>
+      <c r="B14" s="27"/>
     </row>
     <row r="15" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="29"/>
+      <c r="B15" s="27"/>
     </row>
     <row r="16" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="29"/>
+      <c r="B16" s="27"/>
     </row>
     <row r="17" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="29"/>
+      <c r="B17" s="27"/>
     </row>
     <row r="18" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="28"/>
-      <c r="B18" s="29" t="s">
+      <c r="A18" s="26"/>
+      <c r="B18" s="27" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="30"/>
-      <c r="B19" s="29" t="s">
+      <c r="A19" s="28"/>
+      <c r="B19" s="27" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="59"/>
-      <c r="B20" s="29" t="s">
-        <v>196</v>
+      <c r="A20" s="56"/>
+      <c r="B20" s="27" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="117"/>
-      <c r="B21" s="29" t="s">
-        <v>313</v>
+      <c r="A21" s="114"/>
+      <c r="B21" s="27" t="s">
+        <v>307</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="105"/>
-      <c r="B22" s="29" t="s">
-        <v>295</v>
+      <c r="A22" s="102"/>
+      <c r="B22" s="27" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="43"/>
-      <c r="B23" s="29" t="s">
-        <v>133</v>
+      <c r="A23" s="41"/>
+      <c r="B23" s="27" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="44"/>
-      <c r="B24" s="29" t="s">
-        <v>134</v>
+      <c r="A24" s="42"/>
+      <c r="B24" s="27" t="s">
+        <v>131</v>
       </c>
     </row>
   </sheetData>
@@ -11900,10 +11845,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="32" t="s">
+      <c r="B1" s="30" t="s">
         <v>33</v>
       </c>
     </row>
@@ -12045,7 +11990,7 @@
       <c r="K4" s="13"/>
       <c r="L4" s="13"/>
       <c r="M4" s="14" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="N4" s="13" t="s">
         <v>57</v>
@@ -12094,7 +12039,7 @@
       <c r="K5" s="13"/>
       <c r="L5" s="13"/>
       <c r="M5" s="14" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="N5" s="13" t="s">
         <v>57</v>
@@ -12144,10 +12089,10 @@
       </c>
       <c r="K6" s="13"/>
       <c r="L6" s="13" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="M6" s="14" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N6" s="13" t="s">
         <v>57</v>
@@ -12203,35 +12148,35 @@
       <c r="C8" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="D8" s="33"/>
-      <c r="E8" s="33"/>
-      <c r="F8" s="33"/>
-      <c r="G8" s="33"/>
-      <c r="H8" s="33"/>
-      <c r="I8" s="33"/>
-      <c r="J8" s="33"/>
-      <c r="K8" s="33"/>
-      <c r="L8" s="33"/>
-      <c r="M8" s="33"/>
-      <c r="N8" s="33"/>
-      <c r="O8" s="33"/>
-      <c r="P8" s="33"/>
-      <c r="Q8" s="33"/>
-      <c r="R8" s="33"/>
-      <c r="S8" s="33"/>
-      <c r="T8" s="33"/>
-      <c r="U8" s="33"/>
+      <c r="D8" s="31"/>
+      <c r="E8" s="31"/>
+      <c r="F8" s="31"/>
+      <c r="G8" s="31"/>
+      <c r="H8" s="31"/>
+      <c r="I8" s="31"/>
+      <c r="J8" s="31"/>
+      <c r="K8" s="31"/>
+      <c r="L8" s="31"/>
+      <c r="M8" s="31"/>
+      <c r="N8" s="31"/>
+      <c r="O8" s="31"/>
+      <c r="P8" s="31"/>
+      <c r="Q8" s="31"/>
+      <c r="R8" s="31"/>
+      <c r="S8" s="31"/>
+      <c r="T8" s="31"/>
+      <c r="U8" s="31"/>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A9" s="134" t="str">
+      <c r="A9" s="131" t="str">
         <f>'M-CitaServicio'!E3</f>
         <v>Combinación única</v>
       </c>
-      <c r="B9" s="135" t="str">
+      <c r="B9" s="132" t="str">
         <f>'M-CitaServicio'!E2</f>
         <v>Combinación única que indica que un mismo servicio no puede repetirse dos veces dentro de la misma cita</v>
       </c>
-      <c r="C9" s="34" t="str">
+      <c r="C9" s="32" t="str">
         <f>A4</f>
         <v>cita</v>
       </c>
@@ -12255,9 +12200,9 @@
       <c r="U9" s="4"/>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A10" s="134"/>
-      <c r="B10" s="134"/>
-      <c r="C10" s="34" t="str">
+      <c r="A10" s="131"/>
+      <c r="B10" s="131"/>
+      <c r="C10" s="32" t="str">
         <f>A5</f>
         <v>servicio</v>
       </c>
@@ -12307,275 +12252,275 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="106" t="s">
+      <c r="A1" s="103" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="106" t="s">
+      <c r="B1" s="103" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="41.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="107" t="s">
+      <c r="A2" s="104" t="s">
         <v>66</v>
       </c>
-      <c r="B2" s="107" t="s">
-        <v>315</v>
-      </c>
-      <c r="C2" s="108" t="s">
-        <v>316</v>
-      </c>
-      <c r="D2" s="108" t="s">
-        <v>317</v>
-      </c>
-      <c r="E2" s="108" t="s">
-        <v>318</v>
+      <c r="B2" s="104" t="s">
+        <v>309</v>
+      </c>
+      <c r="C2" s="105" t="s">
+        <v>310</v>
+      </c>
+      <c r="D2" s="105" t="s">
+        <v>311</v>
+      </c>
+      <c r="E2" s="105" t="s">
+        <v>312</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="118" t="s">
+      <c r="A3" s="115" t="s">
         <v>70</v>
       </c>
-      <c r="B3" s="48" t="s">
-        <v>319</v>
-      </c>
-      <c r="C3" s="48" t="s">
-        <v>242</v>
-      </c>
-      <c r="D3" s="119" t="s">
-        <v>320</v>
-      </c>
-      <c r="E3" s="113" t="s">
-        <v>149</v>
+      <c r="B3" s="46" t="s">
+        <v>313</v>
+      </c>
+      <c r="C3" s="46" t="s">
+        <v>236</v>
+      </c>
+      <c r="D3" s="116" t="s">
+        <v>314</v>
+      </c>
+      <c r="E3" s="110" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="26">
+      <c r="A4" s="24">
         <v>1</v>
       </c>
-      <c r="B4" s="115" t="str">
+      <c r="B4" s="112" t="str">
         <f>'M-Cita'!G4</f>
         <v>Juan-Fernando-García-Lopez-+57-3245627890-Lunes-10:00-16:00-03/05/2025-1/01/1000-31/08/2026/10:00</v>
       </c>
-      <c r="C4" s="114" t="str">
+      <c r="C4" s="111" t="str">
         <f>'M-Servicio'!G4</f>
         <v>Motilada</v>
       </c>
-      <c r="D4" s="26">
+      <c r="D4" s="24">
         <v>22000</v>
       </c>
-      <c r="E4" s="80" t="str">
+      <c r="E4" s="77" t="str">
         <f t="shared" ref="E4:E13" si="0">_xlfn.CONCAT(B4,"-",C4)</f>
         <v>Juan-Fernando-García-Lopez-+57-3245627890-Lunes-10:00-16:00-03/05/2025-1/01/1000-31/08/2026/10:00-Motilada</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="26">
+      <c r="A5" s="24">
         <v>2</v>
       </c>
-      <c r="B5" s="115" t="str">
+      <c r="B5" s="112" t="str">
         <f>'M-Cita'!G5</f>
         <v>Juan-David-Ortiz-Sanchez-+57-3124518923-Martes-09:00-15:00-02/03/2025-1/01/1000-10/03/2026/09:30</v>
       </c>
-      <c r="C5" s="114" t="str">
+      <c r="C5" s="111" t="str">
         <f>'M-Servicio'!G5</f>
         <v>Corte de barba</v>
       </c>
-      <c r="D5" s="26">
+      <c r="D5" s="24">
         <v>12000</v>
       </c>
-      <c r="E5" s="80" t="str">
+      <c r="E5" s="77" t="str">
         <f t="shared" si="0"/>
         <v>Juan-David-Ortiz-Sanchez-+57-3124518923-Martes-09:00-15:00-02/03/2025-1/01/1000-10/03/2026/09:30-Corte de barba</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="26">
+      <c r="A6" s="24">
         <v>3</v>
       </c>
-      <c r="B6" s="115" t="str">
+      <c r="B6" s="112" t="str">
         <f>'M-Cita'!G5</f>
         <v>Juan-David-Ortiz-Sanchez-+57-3124518923-Martes-09:00-15:00-02/03/2025-1/01/1000-10/03/2026/09:30</v>
       </c>
-      <c r="C6" s="114" t="str">
+      <c r="C6" s="111" t="str">
         <f>'M-Servicio'!G4</f>
         <v>Motilada</v>
       </c>
-      <c r="D6" s="26">
+      <c r="D6" s="24">
         <v>22000</v>
       </c>
-      <c r="E6" s="80" t="str">
+      <c r="E6" s="77" t="str">
         <f t="shared" si="0"/>
         <v>Juan-David-Ortiz-Sanchez-+57-3124518923-Martes-09:00-15:00-02/03/2025-1/01/1000-10/03/2026/09:30-Motilada</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="26">
+      <c r="A7" s="24">
         <v>4</v>
       </c>
-      <c r="B7" s="115" t="str">
+      <c r="B7" s="112" t="str">
         <f>'M-Cita'!G6</f>
         <v>Carlos--Arbeladez--+57-3214533321-Jueves-13:00-19:00-22/12/2022-1/01/1000-14/05/2026/13:00</v>
       </c>
-      <c r="C7" s="114" t="str">
+      <c r="C7" s="111" t="str">
         <f>'M-Servicio'!G6</f>
         <v>Perfilada de barba</v>
       </c>
-      <c r="D7" s="26">
+      <c r="D7" s="24">
         <v>15000</v>
       </c>
-      <c r="E7" s="80" t="str">
+      <c r="E7" s="77" t="str">
         <f t="shared" si="0"/>
         <v>Carlos--Arbeladez--+57-3214533321-Jueves-13:00-19:00-22/12/2022-1/01/1000-14/05/2026/13:00-Perfilada de barba</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="26">
+      <c r="A8" s="24">
         <v>5</v>
       </c>
-      <c r="B8" s="115" t="str">
+      <c r="B8" s="112" t="str">
         <f>'M-Cita'!G7</f>
         <v>Andres--Ramirez-Patiño-+91-9876543210-Sábado-08:00-14:00-15/09/2025-01/01/2026-22/11/2025/13:00</v>
       </c>
-      <c r="C8" s="115" t="str">
+      <c r="C8" s="112" t="str">
         <f>'M-Servicio'!G7</f>
         <v>Arreglo completo de barba con toalla caliente</v>
       </c>
-      <c r="D8" s="26">
+      <c r="D8" s="24">
         <v>35000</v>
       </c>
-      <c r="E8" s="80" t="str">
+      <c r="E8" s="77" t="str">
         <f t="shared" si="0"/>
         <v>Andres--Ramirez-Patiño-+91-9876543210-Sábado-08:00-14:00-15/09/2025-01/01/2026-22/11/2025/13:00-Arreglo completo de barba con toalla caliente</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="26">
+      <c r="A9" s="24">
         <v>6</v>
       </c>
-      <c r="B9" s="115" t="str">
+      <c r="B9" s="112" t="str">
         <f>'M-Cita'!G8</f>
         <v>Carlos--Arbeladez--+57-3214533321-Jueves-13:00-19:00-22/12/2022-1/01/1000-06/08/2026/18:00</v>
       </c>
-      <c r="C9" s="114" t="str">
+      <c r="C9" s="111" t="str">
         <f>'M-Servicio'!G5</f>
         <v>Corte de barba</v>
       </c>
-      <c r="D9" s="26">
+      <c r="D9" s="24">
         <v>12000</v>
       </c>
-      <c r="E9" s="80" t="str">
+      <c r="E9" s="77" t="str">
         <f t="shared" si="0"/>
         <v>Carlos--Arbeladez--+57-3214533321-Jueves-13:00-19:00-22/12/2022-1/01/1000-06/08/2026/18:00-Corte de barba</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="26">
+      <c r="A10" s="24">
         <v>7</v>
       </c>
-      <c r="B10" s="115" t="str">
+      <c r="B10" s="112" t="str">
         <f>'M-Cita'!G9</f>
         <v>Juan-David-Ortiz-Sanchez-+57-3124518923-Martes-09:00-15:00-02/03/2025-1/01/1000-01/09/2026/14:00</v>
       </c>
-      <c r="C10" s="114" t="str">
+      <c r="C10" s="111" t="str">
         <f>'M-Servicio'!G5</f>
         <v>Corte de barba</v>
       </c>
-      <c r="D10" s="26">
+      <c r="D10" s="24">
         <v>12000</v>
       </c>
-      <c r="E10" s="80" t="str">
+      <c r="E10" s="77" t="str">
         <f t="shared" si="0"/>
         <v>Juan-David-Ortiz-Sanchez-+57-3124518923-Martes-09:00-15:00-02/03/2025-1/01/1000-01/09/2026/14:00-Corte de barba</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="26">
+      <c r="A11" s="24">
         <v>8</v>
       </c>
-      <c r="B11" s="115" t="str">
+      <c r="B11" s="112" t="str">
         <f>'M-Cita'!G10</f>
         <v>Juan-Fernando-García-Lopez-+57-3245627890-Lunes-10:00-16:00-03/05/2025-1/01/1000-01/06/2026/10:00</v>
       </c>
-      <c r="C11" s="114" t="str">
+      <c r="C11" s="111" t="str">
         <f>'M-Servicio'!G4</f>
         <v>Motilada</v>
       </c>
-      <c r="D11" s="26">
+      <c r="D11" s="24">
         <v>22000</v>
       </c>
-      <c r="E11" s="80" t="str">
+      <c r="E11" s="77" t="str">
         <f t="shared" si="0"/>
         <v>Juan-Fernando-García-Lopez-+57-3245627890-Lunes-10:00-16:00-03/05/2025-1/01/1000-01/06/2026/10:00-Motilada</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="26">
+      <c r="A12" s="24">
         <v>9</v>
       </c>
-      <c r="B12" s="115" t="str">
+      <c r="B12" s="112" t="str">
         <f>'M-Cita'!G11</f>
         <v>Juan-David-Ortiz-Sanchez-+57-3124518923-Martes-09:00-15:00-02/03/2025-1/01/1000-16/06/2026/09:00</v>
       </c>
-      <c r="C12" s="114" t="str">
+      <c r="C12" s="111" t="str">
         <f>'M-Servicio'!G5</f>
         <v>Corte de barba</v>
       </c>
-      <c r="D12" s="26">
+      <c r="D12" s="24">
         <v>12000</v>
       </c>
-      <c r="E12" s="80" t="str">
+      <c r="E12" s="77" t="str">
         <f t="shared" si="0"/>
         <v>Juan-David-Ortiz-Sanchez-+57-3124518923-Martes-09:00-15:00-02/03/2025-1/01/1000-16/06/2026/09:00-Corte de barba</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="26">
+      <c r="A13" s="24">
         <v>10</v>
       </c>
-      <c r="B13" s="115" t="str">
+      <c r="B13" s="112" t="str">
         <f>'M-Cita'!G12</f>
         <v>Carlos--Arbeladez--+57-3214533321-Jueves-13:00-19:00-22/12/2022-1/01/1000-02/07/2026/15:00</v>
       </c>
-      <c r="C13" s="114" t="str">
+      <c r="C13" s="111" t="str">
         <f>'M-Servicio'!G6</f>
         <v>Perfilada de barba</v>
       </c>
-      <c r="D13" s="26">
+      <c r="D13" s="24">
         <v>15000</v>
       </c>
-      <c r="E13" s="80" t="str">
+      <c r="E13" s="77" t="str">
         <f t="shared" si="0"/>
         <v>Carlos--Arbeladez--+57-3214533321-Jueves-13:00-19:00-22/12/2022-1/01/1000-02/07/2026/15:00-Perfilada de barba</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19" s="120"/>
+      <c r="A19" s="117"/>
       <c r="B19" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="121"/>
-      <c r="B20" s="29" t="s">
+      <c r="A20" s="118"/>
+      <c r="B20" s="27" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="122"/>
-      <c r="B21" s="29" t="s">
-        <v>233</v>
+      <c r="A21" s="119"/>
+      <c r="B21" s="27" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22" s="123"/>
+      <c r="A22" s="120"/>
       <c r="B22" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23" s="124"/>
+      <c r="A23" s="121"/>
       <c r="B23" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
   </sheetData>
@@ -12630,10 +12575,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="32" t="s">
+      <c r="B1" s="30" t="s">
         <v>33</v>
       </c>
     </row>
@@ -12775,7 +12720,7 @@
       <c r="K4" s="13"/>
       <c r="L4" s="13"/>
       <c r="M4" s="14" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="N4" s="13" t="s">
         <v>57</v>
@@ -12824,7 +12769,7 @@
       <c r="K5" s="13"/>
       <c r="L5" s="13"/>
       <c r="M5" s="14" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="N5" s="13" t="s">
         <v>57</v>
@@ -12874,10 +12819,10 @@
       </c>
       <c r="K6" s="13"/>
       <c r="L6" s="13" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="M6" s="14" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="N6" s="13" t="s">
         <v>55</v>
@@ -12930,7 +12875,7 @@
       <c r="K7" s="13"/>
       <c r="L7" s="13"/>
       <c r="M7" s="14" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="N7" s="13" t="s">
         <v>55</v>
@@ -12966,7 +12911,7 @@
         <v>57</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E8" s="13" t="s">
         <v>55</v>
@@ -12996,7 +12941,7 @@
         <v>57</v>
       </c>
       <c r="T8" s="13" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="U8" s="13" t="s">
         <v>57</v>
@@ -13035,24 +12980,24 @@
       <c r="C10" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="D10" s="33"/>
-      <c r="E10" s="33"/>
-      <c r="F10" s="33"/>
-      <c r="G10" s="33"/>
-      <c r="H10" s="33"/>
-      <c r="I10" s="33"/>
-      <c r="J10" s="33"/>
-      <c r="K10" s="33"/>
-      <c r="L10" s="33"/>
-      <c r="M10" s="33"/>
-      <c r="N10" s="33"/>
-      <c r="O10" s="33"/>
-      <c r="P10" s="33"/>
-      <c r="Q10" s="33"/>
-      <c r="R10" s="33"/>
-      <c r="S10" s="33"/>
-      <c r="T10" s="33"/>
-      <c r="U10" s="33"/>
+      <c r="D10" s="31"/>
+      <c r="E10" s="31"/>
+      <c r="F10" s="31"/>
+      <c r="G10" s="31"/>
+      <c r="H10" s="31"/>
+      <c r="I10" s="31"/>
+      <c r="J10" s="31"/>
+      <c r="K10" s="31"/>
+      <c r="L10" s="31"/>
+      <c r="M10" s="31"/>
+      <c r="N10" s="31"/>
+      <c r="O10" s="31"/>
+      <c r="P10" s="31"/>
+      <c r="Q10" s="31"/>
+      <c r="R10" s="31"/>
+      <c r="S10" s="31"/>
+      <c r="T10" s="31"/>
+      <c r="U10" s="31"/>
     </row>
     <row r="11" spans="1:21" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="str">
@@ -13063,7 +13008,7 @@
         <f>'M-Multa'!G2</f>
         <v>Combinación única que indica que una misma cita no puede generar más de una multa</v>
       </c>
-      <c r="C11" s="34" t="str">
+      <c r="C11" s="32" t="str">
         <f>A5</f>
         <v>cita</v>
       </c>
@@ -13120,228 +13065,228 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="106" t="s">
+      <c r="A1" s="103" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="106" t="s">
+      <c r="B1" s="103" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="107" t="s">
+      <c r="A2" s="104" t="s">
         <v>66</v>
       </c>
-      <c r="B2" s="107" t="s">
+      <c r="B2" s="104" t="s">
+        <v>317</v>
+      </c>
+      <c r="C2" s="105" t="s">
+        <v>318</v>
+      </c>
+      <c r="D2" s="105" t="s">
+        <v>319</v>
+      </c>
+      <c r="E2" s="105" t="s">
+        <v>320</v>
+      </c>
+      <c r="F2" s="105" t="s">
+        <v>321</v>
+      </c>
+      <c r="G2" s="105" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="106" t="s">
+        <v>70</v>
+      </c>
+      <c r="B3" s="46" t="s">
+        <v>299</v>
+      </c>
+      <c r="C3" s="46" t="s">
+        <v>313</v>
+      </c>
+      <c r="D3" s="108" t="s">
         <v>323</v>
       </c>
-      <c r="C2" s="108" t="s">
+      <c r="E3" s="122" t="s">
         <v>324</v>
       </c>
-      <c r="D2" s="108" t="s">
+      <c r="F3" s="123" t="s">
         <v>325</v>
       </c>
-      <c r="E2" s="108" t="s">
-        <v>326</v>
-      </c>
-      <c r="F2" s="108" t="s">
-        <v>327</v>
-      </c>
-      <c r="G2" s="108" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="109" t="s">
-        <v>70</v>
-      </c>
-      <c r="B3" s="48" t="s">
-        <v>305</v>
-      </c>
-      <c r="C3" s="48" t="s">
-        <v>319</v>
-      </c>
-      <c r="D3" s="111" t="s">
-        <v>329</v>
-      </c>
-      <c r="E3" s="125" t="s">
-        <v>330</v>
-      </c>
-      <c r="F3" s="126" t="s">
-        <v>331</v>
-      </c>
-      <c r="G3" s="127" t="s">
-        <v>149</v>
+      <c r="G3" s="124" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="26">
+      <c r="A4" s="24">
         <v>1</v>
       </c>
-      <c r="B4" s="115" t="str">
+      <c r="B4" s="112" t="str">
         <f>'M-Cliente'!J6</f>
         <v>Simon--Ochoa-Ramirez-+57-3119884321</v>
       </c>
-      <c r="C4" s="115" t="str">
+      <c r="C4" s="112" t="str">
         <f>'M-Cita'!G6</f>
         <v>Carlos--Arbeladez--+57-3214533321-Jueves-13:00-19:00-22/12/2022-1/01/1000-14/05/2026/13:00</v>
       </c>
-      <c r="D4" s="64">
+      <c r="D4" s="61">
         <f>'M-Regla'!D4</f>
         <v>10000</v>
       </c>
-      <c r="E4" s="26" t="s">
-        <v>310</v>
-      </c>
-      <c r="F4" s="26" t="s">
-        <v>112</v>
-      </c>
-      <c r="G4" s="80" t="str">
+      <c r="E4" s="24" t="s">
+        <v>304</v>
+      </c>
+      <c r="F4" s="24" t="s">
+        <v>109</v>
+      </c>
+      <c r="G4" s="77" t="str">
         <f>C4</f>
         <v>Carlos--Arbeladez--+57-3214533321-Jueves-13:00-19:00-22/12/2022-1/01/1000-14/05/2026/13:00</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="26">
+      <c r="A5" s="24">
         <v>2</v>
       </c>
-      <c r="B5" s="115" t="str">
+      <c r="B5" s="112" t="str">
         <f>'M-Cliente'!J7</f>
         <v>Alexis--Gallego--+58-4127359182</v>
       </c>
-      <c r="C5" s="115" t="str">
+      <c r="C5" s="112" t="str">
         <f>'M-Cita'!G7</f>
         <v>Andres--Ramirez-Patiño-+91-9876543210-Sábado-08:00-14:00-15/09/2025-01/01/2026-22/11/2025/13:00</v>
       </c>
-      <c r="D5" s="26">
+      <c r="D5" s="24">
         <f>'M-CitaServicio'!D8</f>
         <v>35000</v>
       </c>
-      <c r="E5" s="26" t="s">
-        <v>311</v>
-      </c>
-      <c r="F5" s="26" t="s">
-        <v>127</v>
-      </c>
-      <c r="G5" s="80" t="str">
+      <c r="E5" s="24" t="s">
+        <v>305</v>
+      </c>
+      <c r="F5" s="24" t="s">
+        <v>124</v>
+      </c>
+      <c r="G5" s="77" t="str">
         <f>C5</f>
         <v>Andres--Ramirez-Patiño-+91-9876543210-Sábado-08:00-14:00-15/09/2025-01/01/2026-22/11/2025/13:00</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="26">
+      <c r="A6" s="24">
         <v>3</v>
       </c>
-      <c r="B6" s="115" t="str">
+      <c r="B6" s="112" t="str">
         <f>'M-Cliente'!J8</f>
         <v>Kevin-Andrés-Muñoz-Salazar-+57-3005544332</v>
       </c>
-      <c r="C6" s="115" t="str">
+      <c r="C6" s="112" t="str">
         <f>'M-Cita'!G10</f>
         <v>Juan-Fernando-García-Lopez-+57-3245627890-Lunes-10:00-16:00-03/05/2025-1/01/1000-01/06/2026/10:00</v>
       </c>
-      <c r="D6" s="26">
+      <c r="D6" s="24">
         <f>'M-CitaServicio'!D11</f>
         <v>22000</v>
       </c>
-      <c r="E6" s="26" t="s">
-        <v>311</v>
-      </c>
-      <c r="F6" s="26" t="s">
-        <v>127</v>
-      </c>
-      <c r="G6" s="80" t="str">
+      <c r="E6" s="24" t="s">
+        <v>305</v>
+      </c>
+      <c r="F6" s="24" t="s">
+        <v>124</v>
+      </c>
+      <c r="G6" s="77" t="str">
         <f>C6</f>
         <v>Juan-Fernando-García-Lopez-+57-3245627890-Lunes-10:00-16:00-03/05/2025-1/01/1000-01/06/2026/10:00</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="26">
+      <c r="A7" s="24">
         <v>4</v>
       </c>
-      <c r="B7" s="115" t="str">
+      <c r="B7" s="112" t="str">
         <f>'M-Cliente'!J8</f>
         <v>Kevin-Andrés-Muñoz-Salazar-+57-3005544332</v>
       </c>
-      <c r="C7" s="115" t="str">
+      <c r="C7" s="112" t="str">
         <f>'M-Cita'!G11</f>
         <v>Juan-David-Ortiz-Sanchez-+57-3124518923-Martes-09:00-15:00-02/03/2025-1/01/1000-16/06/2026/09:00</v>
       </c>
-      <c r="D7" s="26">
+      <c r="D7" s="24">
         <f>'M-CitaServicio'!D12</f>
         <v>12000</v>
       </c>
-      <c r="E7" s="26" t="s">
-        <v>311</v>
-      </c>
-      <c r="F7" s="26" t="s">
-        <v>127</v>
-      </c>
-      <c r="G7" s="80" t="str">
+      <c r="E7" s="24" t="s">
+        <v>305</v>
+      </c>
+      <c r="F7" s="24" t="s">
+        <v>124</v>
+      </c>
+      <c r="G7" s="77" t="str">
         <f>C7</f>
         <v>Juan-David-Ortiz-Sanchez-+57-3124518923-Martes-09:00-15:00-02/03/2025-1/01/1000-16/06/2026/09:00</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="26">
+      <c r="A8" s="24">
         <v>5</v>
       </c>
-      <c r="B8" s="115" t="str">
+      <c r="B8" s="112" t="str">
         <f>'M-Cliente'!J8</f>
         <v>Kevin-Andrés-Muñoz-Salazar-+57-3005544332</v>
       </c>
-      <c r="C8" s="115" t="str">
+      <c r="C8" s="112" t="str">
         <f>'M-Cita'!G12</f>
         <v>Carlos--Arbeladez--+57-3214533321-Jueves-13:00-19:00-22/12/2022-1/01/1000-02/07/2026/15:00</v>
       </c>
-      <c r="D8" s="26">
+      <c r="D8" s="24">
         <f>'M-CitaServicio'!D13</f>
         <v>15000</v>
       </c>
-      <c r="E8" s="26" t="s">
-        <v>311</v>
-      </c>
-      <c r="F8" s="26" t="s">
-        <v>127</v>
-      </c>
-      <c r="G8" s="80" t="str">
+      <c r="E8" s="24" t="s">
+        <v>305</v>
+      </c>
+      <c r="F8" s="24" t="s">
+        <v>124</v>
+      </c>
+      <c r="G8" s="77" t="str">
         <f>C8</f>
         <v>Carlos--Arbeladez--+57-3214533321-Jueves-13:00-19:00-22/12/2022-1/01/1000-02/07/2026/15:00</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="120"/>
-      <c r="B14" s="29" t="s">
+      <c r="A14" s="117"/>
+      <c r="B14" s="27" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="128"/>
-      <c r="B15" s="29" t="s">
+      <c r="A15" s="125"/>
+      <c r="B15" s="27" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="122"/>
-      <c r="B16" s="29" t="s">
-        <v>233</v>
+      <c r="A16" s="119"/>
+      <c r="B16" s="27" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="129"/>
-      <c r="B17" s="29" t="s">
-        <v>133</v>
+      <c r="A17" s="126"/>
+      <c r="B17" s="27" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" s="130"/>
+      <c r="A18" s="127"/>
       <c r="B18" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19" s="131"/>
+      <c r="A19" s="128"/>
       <c r="B19" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
   </sheetData>
@@ -13371,61 +13316,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="106" t="s">
+      <c r="A1" s="103" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="106" t="s">
+      <c r="B1" s="103" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="107" t="s">
+      <c r="A2" s="104" t="s">
         <v>66</v>
       </c>
-      <c r="B2" s="107"/>
-      <c r="C2" s="107"/>
+      <c r="B2" s="104"/>
+      <c r="C2" s="104"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="109" t="s">
+      <c r="A3" s="106" t="s">
         <v>70</v>
       </c>
-      <c r="B3" s="132"/>
-      <c r="C3" s="132"/>
+      <c r="B3" s="129"/>
+      <c r="C3" s="129"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="26">
+      <c r="A4" s="24">
         <v>1</v>
       </c>
-      <c r="B4" s="133"/>
-      <c r="C4" s="133"/>
+      <c r="B4" s="130"/>
+      <c r="C4" s="130"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="26">
+      <c r="A5" s="24">
         <v>2</v>
       </c>
-      <c r="B5" s="133"/>
-      <c r="C5" s="133"/>
+      <c r="B5" s="130"/>
+      <c r="C5" s="130"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="26">
+      <c r="A6" s="24">
         <v>3</v>
       </c>
-      <c r="B6" s="133"/>
-      <c r="C6" s="133"/>
+      <c r="B6" s="130"/>
+      <c r="C6" s="130"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="26">
+      <c r="A7" s="24">
         <v>4</v>
       </c>
-      <c r="B7" s="133"/>
-      <c r="C7" s="133"/>
+      <c r="B7" s="130"/>
+      <c r="C7" s="130"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="26">
+      <c r="A8" s="24">
         <v>5</v>
       </c>
-      <c r="B8" s="133"/>
-      <c r="C8" s="133"/>
+      <c r="B8" s="130"/>
+      <c r="C8" s="130"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -13461,7 +13406,7 @@
     <col min="9" max="9" width="20.6640625" customWidth="1"/>
     <col min="10" max="10" width="21.88671875" customWidth="1"/>
     <col min="11" max="11" width="20.33203125" customWidth="1"/>
-    <col min="12" max="12" width="17.6640625" customWidth="1"/>
+    <col min="12" max="12" width="28.109375" customWidth="1"/>
     <col min="13" max="13" width="26.6640625" customWidth="1"/>
     <col min="14" max="14" width="14.33203125" customWidth="1"/>
     <col min="15" max="15" width="29.6640625" customWidth="1"/>
@@ -13621,7 +13566,9 @@
       <c r="I4" s="13"/>
       <c r="J4" s="13"/>
       <c r="K4" s="13"/>
-      <c r="L4" s="13"/>
+      <c r="L4" s="14" t="s">
+        <v>327</v>
+      </c>
       <c r="M4" s="14" t="s">
         <v>59</v>
       </c>
@@ -13646,7 +13593,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="5" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:21" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A5" s="13" t="str">
         <f>'M-Dueño'!C3</f>
         <v>contraseña</v>
@@ -13665,7 +13612,7 @@
         <v>55</v>
       </c>
       <c r="F5" s="13">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="G5" s="13">
         <v>60</v>
@@ -13721,7 +13668,7 @@
         <v>1</v>
       </c>
       <c r="G6" s="13">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="H6" s="13"/>
       <c r="I6" s="13"/>
@@ -13791,13 +13738,13 @@
       <c r="U8" s="18"/>
     </row>
     <row r="9" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="134" t="s">
+      <c r="A9" s="131" t="s">
         <v>64</v>
       </c>
-      <c r="B9" s="135" t="s">
+      <c r="B9" s="132" t="s">
         <v>65</v>
       </c>
-      <c r="C9" s="19" t="str">
+      <c r="C9" s="133" t="str">
         <f>A4</f>
         <v>correo</v>
       </c>
@@ -13821,9 +13768,9 @@
       <c r="U9" s="16"/>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A10" s="134"/>
-      <c r="B10" s="134"/>
-      <c r="C10" s="20"/>
+      <c r="A10" s="131"/>
+      <c r="B10" s="131"/>
+      <c r="C10" s="134"/>
       <c r="D10" s="16"/>
       <c r="E10" s="16"/>
       <c r="F10" s="16"/>
@@ -13844,9 +13791,10 @@
       <c r="U10" s="16"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A9:A10"/>
     <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:C10"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1" location="'Modelo de Dominio'!A1" display="&lt;&lt;&lt;&lt; Ir al modulo de dominio" xr:uid="{00000000-0004-0000-0200-000000000000}"/>
@@ -13877,65 +13825,65 @@
       </c>
     </row>
     <row r="2" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="19" t="s">
         <v>66</v>
       </c>
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="19" t="s">
         <v>67</v>
       </c>
-      <c r="C2" s="21" t="s">
+      <c r="C2" s="19" t="s">
         <v>68</v>
       </c>
-      <c r="D2" s="21" t="s">
+      <c r="D2" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="E2" s="22"/>
+      <c r="E2" s="20"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="23" t="s">
+      <c r="A3" s="21" t="s">
         <v>70</v>
       </c>
-      <c r="B3" s="24" t="s">
+      <c r="B3" s="22" t="s">
         <v>71</v>
       </c>
-      <c r="C3" s="24" t="s">
+      <c r="C3" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="D3" s="25" t="s">
+      <c r="D3" s="23" t="s">
         <v>73</v>
       </c>
-      <c r="E3" s="22"/>
+      <c r="E3" s="20"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="26">
+      <c r="A4" s="24">
         <v>1</v>
       </c>
-      <c r="B4" s="27" t="s">
+      <c r="B4" s="25" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="26" t="s">
+      <c r="C4" s="24" t="s">
         <v>75</v>
       </c>
-      <c r="D4" s="26" t="s">
+      <c r="D4" s="24" t="s">
         <v>76</v>
       </c>
-      <c r="E4" s="22"/>
+      <c r="E4" s="20"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="28"/>
-      <c r="B10" s="29" t="s">
+      <c r="A10" s="26"/>
+      <c r="B10" s="27" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="30"/>
-      <c r="B11" s="29" t="s">
+      <c r="A11" s="28"/>
+      <c r="B11" s="27" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="31"/>
-      <c r="B12" s="29" t="s">
+      <c r="A12" s="29"/>
+      <c r="B12" s="27" t="s">
         <v>79</v>
       </c>
     </row>
@@ -13977,10 +13925,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="32" t="s">
+      <c r="B1" s="30" t="s">
         <v>33</v>
       </c>
     </row>
@@ -14109,7 +14057,7 @@
         <v>57</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="E4" s="13" t="s">
         <v>55</v>
@@ -14160,7 +14108,7 @@
         <v>57</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="E5" s="13" t="s">
         <v>57</v>
@@ -14211,7 +14159,7 @@
         <v>57</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="E6" s="13" t="s">
         <v>55</v>
@@ -14262,7 +14210,7 @@
         <v>57</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="E7" s="13" t="s">
         <v>57</v>
@@ -14340,20 +14288,22 @@
       </c>
       <c r="P8" s="13"/>
       <c r="Q8" s="13" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="R8" s="13" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="S8" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="T8" s="13"/>
+      <c r="T8" s="135" t="s">
+        <v>328</v>
+      </c>
       <c r="U8" s="13" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="9" spans="1:21" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:21" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A9" s="13" t="str">
         <f>'M-Barbero'!G3</f>
         <v>celular</v>
@@ -14366,25 +14316,25 @@
         <v>57</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>82</v>
+        <v>58</v>
       </c>
       <c r="E9" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="F9" s="13"/>
-      <c r="G9" s="13"/>
+      <c r="F9" s="13">
+        <v>4</v>
+      </c>
+      <c r="G9" s="13">
+        <v>15</v>
+      </c>
       <c r="H9" s="13"/>
       <c r="I9" s="13"/>
-      <c r="J9" s="13">
-        <v>3000000000</v>
-      </c>
-      <c r="K9" s="13">
-        <v>3999999999</v>
-      </c>
-      <c r="L9" s="13"/>
-      <c r="M9" s="14" t="s">
-        <v>83</v>
-      </c>
+      <c r="J9" s="13"/>
+      <c r="K9" s="13"/>
+      <c r="L9" s="14" t="s">
+        <v>329</v>
+      </c>
+      <c r="M9" s="14"/>
       <c r="N9" s="13" t="s">
         <v>57</v>
       </c>
@@ -14393,20 +14343,22 @@
       </c>
       <c r="P9" s="13"/>
       <c r="Q9" s="13" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="R9" s="13" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="S9" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="T9" s="13"/>
+      <c r="T9" s="135" t="s">
+        <v>330</v>
+      </c>
       <c r="U9" s="13" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="10" spans="1:21" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:21" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A10" s="13" t="str">
         <f>'M-Barbero'!H3</f>
         <v>correo</v>
@@ -14434,9 +14386,11 @@
       <c r="I10" s="13"/>
       <c r="J10" s="13"/>
       <c r="K10" s="13"/>
-      <c r="L10" s="13"/>
+      <c r="L10" s="14" t="s">
+        <v>327</v>
+      </c>
       <c r="M10" s="14" t="s">
-        <v>84</v>
+        <v>59</v>
       </c>
       <c r="N10" s="13" t="s">
         <v>57</v>
@@ -14478,7 +14432,7 @@
         <v>55</v>
       </c>
       <c r="F11" s="13">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="G11" s="13">
         <v>60</v>
@@ -14525,10 +14479,10 @@
         <v>57</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F12" s="13"/>
       <c r="G12" s="13"/>
@@ -14538,7 +14492,7 @@
       <c r="K12" s="13"/>
       <c r="L12" s="13"/>
       <c r="M12" s="14" t="s">
-        <v>86</v>
+        <v>331</v>
       </c>
       <c r="N12" s="13" t="s">
         <v>55</v>
@@ -14594,35 +14548,35 @@
       <c r="C14" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="D14" s="33"/>
-      <c r="E14" s="33"/>
-      <c r="F14" s="33"/>
-      <c r="G14" s="33"/>
-      <c r="H14" s="33"/>
-      <c r="I14" s="33"/>
-      <c r="J14" s="33"/>
-      <c r="K14" s="33"/>
-      <c r="L14" s="33"/>
-      <c r="M14" s="33"/>
-      <c r="N14" s="33"/>
-      <c r="O14" s="33"/>
-      <c r="P14" s="33"/>
-      <c r="Q14" s="33"/>
-      <c r="R14" s="33"/>
-      <c r="S14" s="33"/>
-      <c r="T14" s="33"/>
-      <c r="U14" s="33"/>
+      <c r="D14" s="136"/>
+      <c r="E14" s="136"/>
+      <c r="F14" s="136"/>
+      <c r="G14" s="136"/>
+      <c r="H14" s="136"/>
+      <c r="I14" s="136"/>
+      <c r="J14" s="136"/>
+      <c r="K14" s="136"/>
+      <c r="L14" s="136"/>
+      <c r="M14" s="136"/>
+      <c r="N14" s="136"/>
+      <c r="O14" s="136"/>
+      <c r="P14" s="136"/>
+      <c r="Q14" s="136"/>
+      <c r="R14" s="136"/>
+      <c r="S14" s="136"/>
+      <c r="T14" s="136"/>
+      <c r="U14" s="136"/>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A15" s="134" t="str">
+      <c r="A15" s="131" t="str">
         <f>'M-Barbero'!K3</f>
         <v xml:space="preserve">Combinación única </v>
       </c>
-      <c r="B15" s="135" t="str">
+      <c r="B15" s="132" t="str">
         <f>'M-Barbero'!K2</f>
         <v>Combinacion única que indica que no puede existir más de un barbero con el mismo nombre, apellidos, prefijo de celular y número de celular</v>
       </c>
-      <c r="C15" s="34" t="str">
+      <c r="C15" s="32" t="str">
         <f t="shared" ref="C15:C20" si="0">A4</f>
         <v>primerNombre</v>
       </c>
@@ -14646,9 +14600,9 @@
       <c r="U15" s="4"/>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A16" s="134"/>
-      <c r="B16" s="134"/>
-      <c r="C16" s="34" t="str">
+      <c r="A16" s="131"/>
+      <c r="B16" s="131"/>
+      <c r="C16" s="32" t="str">
         <f t="shared" si="0"/>
         <v>segundoNombre</v>
       </c>
@@ -14672,9 +14626,9 @@
       <c r="U16" s="4"/>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A17" s="134"/>
-      <c r="B17" s="134"/>
-      <c r="C17" s="34" t="str">
+      <c r="A17" s="131"/>
+      <c r="B17" s="131"/>
+      <c r="C17" s="32" t="str">
         <f t="shared" si="0"/>
         <v>primerApellido</v>
       </c>
@@ -14698,9 +14652,9 @@
       <c r="U17" s="4"/>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A18" s="134"/>
-      <c r="B18" s="134"/>
-      <c r="C18" s="34" t="str">
+      <c r="A18" s="131"/>
+      <c r="B18" s="131"/>
+      <c r="C18" s="32" t="str">
         <f t="shared" si="0"/>
         <v>segundoApellido</v>
       </c>
@@ -14724,9 +14678,9 @@
       <c r="U18" s="4"/>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A19" s="134"/>
-      <c r="B19" s="134"/>
-      <c r="C19" s="34" t="str">
+      <c r="A19" s="131"/>
+      <c r="B19" s="131"/>
+      <c r="C19" s="32" t="str">
         <f t="shared" si="0"/>
         <v>prefijo</v>
       </c>
@@ -14750,9 +14704,9 @@
       <c r="U19" s="4"/>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A20" s="134"/>
-      <c r="B20" s="134"/>
-      <c r="C20" s="34" t="str">
+      <c r="A20" s="131"/>
+      <c r="B20" s="131"/>
+      <c r="C20" s="32" t="str">
         <f t="shared" si="0"/>
         <v>celular</v>
       </c>
@@ -14820,277 +14774,277 @@
       <c r="F1" s="5"/>
     </row>
     <row r="2" spans="1:11" ht="41.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="35" t="s">
+      <c r="A2" s="33" t="s">
         <v>66</v>
       </c>
-      <c r="B2" s="35" t="s">
+      <c r="B2" s="33" t="s">
+        <v>84</v>
+      </c>
+      <c r="C2" s="33" t="s">
+        <v>85</v>
+      </c>
+      <c r="D2" s="33" t="s">
+        <v>86</v>
+      </c>
+      <c r="E2" s="33" t="s">
         <v>87</v>
       </c>
-      <c r="C2" s="35" t="s">
+      <c r="F2" s="33" t="s">
         <v>88</v>
       </c>
-      <c r="D2" s="35" t="s">
+      <c r="G2" s="34" t="s">
         <v>89</v>
       </c>
-      <c r="E2" s="35" t="s">
+      <c r="H2" s="34" t="s">
         <v>90</v>
       </c>
-      <c r="F2" s="35" t="s">
+      <c r="I2" s="34" t="s">
         <v>91</v>
       </c>
-      <c r="G2" s="36" t="s">
+      <c r="J2" s="34" t="s">
         <v>92</v>
       </c>
-      <c r="H2" s="36" t="s">
+      <c r="K2" s="35" t="s">
         <v>93</v>
       </c>
-      <c r="I2" s="36" t="s">
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="B3" s="22" t="s">
         <v>94</v>
       </c>
-      <c r="J2" s="36" t="s">
+      <c r="C3" s="22" t="s">
         <v>95</v>
       </c>
-      <c r="K2" s="37" t="s">
+      <c r="D3" s="22" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" s="23" t="s">
-        <v>70</v>
-      </c>
-      <c r="B3" s="24" t="s">
+      <c r="E3" s="22" t="s">
         <v>97</v>
       </c>
-      <c r="C3" s="24" t="s">
+      <c r="F3" s="22" t="s">
         <v>98</v>
       </c>
-      <c r="D3" s="24" t="s">
+      <c r="G3" s="22" t="s">
         <v>99</v>
       </c>
-      <c r="E3" s="24" t="s">
+      <c r="H3" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="I3" s="22" t="s">
+        <v>72</v>
+      </c>
+      <c r="J3" s="36" t="s">
         <v>100</v>
       </c>
-      <c r="F3" s="24" t="s">
+      <c r="K3" s="37" t="s">
         <v>101</v>
       </c>
-      <c r="G3" s="24" t="s">
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4" s="24">
+        <v>1</v>
+      </c>
+      <c r="B4" s="24" t="s">
         <v>102</v>
       </c>
-      <c r="H3" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="I3" s="24" t="s">
-        <v>72</v>
-      </c>
-      <c r="J3" s="38" t="s">
+      <c r="C4" s="24" t="s">
         <v>103</v>
       </c>
-      <c r="K3" s="39" t="s">
+      <c r="D4" s="24" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4" s="26">
-        <v>1</v>
-      </c>
-      <c r="B4" s="26" t="s">
+      <c r="E4" s="24" t="s">
         <v>105</v>
       </c>
-      <c r="C4" s="26" t="s">
+      <c r="F4" s="38" t="s">
         <v>106</v>
       </c>
-      <c r="D4" s="26" t="s">
+      <c r="G4" s="24">
+        <v>3245627890</v>
+      </c>
+      <c r="H4" s="25" t="s">
         <v>107</v>
       </c>
-      <c r="E4" s="26" t="s">
+      <c r="I4" s="39" t="s">
         <v>108</v>
       </c>
-      <c r="F4" s="40" t="s">
+      <c r="J4" s="24" t="s">
         <v>109</v>
       </c>
-      <c r="G4" s="26">
-        <v>3245627890</v>
-      </c>
-      <c r="H4" s="27" t="s">
-        <v>110</v>
-      </c>
-      <c r="I4" s="41" t="s">
-        <v>111</v>
-      </c>
-      <c r="J4" s="26" t="s">
-        <v>112</v>
-      </c>
-      <c r="K4" s="26" t="str">
+      <c r="K4" s="24" t="str">
         <f>_xlfn.CONCAT(B4,"-",C4,"-",D4,"-",E4,"-",F4,"-",G4)</f>
         <v>Juan-Fernando-García-Lopez-+57-3245627890</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A5" s="26">
+      <c r="A5" s="24">
         <v>2</v>
       </c>
-      <c r="B5" s="26" t="s">
-        <v>105</v>
-      </c>
-      <c r="C5" s="26" t="s">
+      <c r="B5" s="24" t="s">
+        <v>102</v>
+      </c>
+      <c r="C5" s="24" t="s">
+        <v>110</v>
+      </c>
+      <c r="D5" s="24" t="s">
+        <v>111</v>
+      </c>
+      <c r="E5" s="24" t="s">
+        <v>112</v>
+      </c>
+      <c r="F5" s="38" t="s">
+        <v>106</v>
+      </c>
+      <c r="G5" s="24">
+        <v>3124518923</v>
+      </c>
+      <c r="H5" s="25" t="s">
         <v>113</v>
       </c>
-      <c r="D5" s="26" t="s">
+      <c r="I5" s="39" t="s">
         <v>114</v>
       </c>
-      <c r="E5" s="26" t="s">
-        <v>115</v>
-      </c>
-      <c r="F5" s="40" t="s">
+      <c r="J5" s="24" t="s">
         <v>109</v>
       </c>
-      <c r="G5" s="26">
-        <v>3124518923</v>
-      </c>
-      <c r="H5" s="27" t="s">
-        <v>116</v>
-      </c>
-      <c r="I5" s="41" t="s">
-        <v>117</v>
-      </c>
-      <c r="J5" s="26" t="s">
-        <v>112</v>
-      </c>
-      <c r="K5" s="26" t="str">
+      <c r="K5" s="24" t="str">
         <f>_xlfn.CONCAT(B5,"-",C5,"-",D5,"-",E5,"-",F5,"-",G5)</f>
         <v>Juan-David-Ortiz-Sanchez-+57-3124518923</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A6" s="26">
+      <c r="A6" s="24">
         <v>3</v>
       </c>
-      <c r="B6" s="26" t="s">
+      <c r="B6" s="24" t="s">
         <v>76</v>
       </c>
-      <c r="C6" s="26"/>
-      <c r="D6" s="26" t="s">
-        <v>118</v>
-      </c>
-      <c r="E6" s="26"/>
-      <c r="F6" s="40" t="s">
+      <c r="C6" s="24"/>
+      <c r="D6" s="24" t="s">
+        <v>115</v>
+      </c>
+      <c r="E6" s="24"/>
+      <c r="F6" s="38" t="s">
+        <v>106</v>
+      </c>
+      <c r="G6" s="24">
+        <v>3214533321</v>
+      </c>
+      <c r="H6" s="25" t="s">
+        <v>116</v>
+      </c>
+      <c r="I6" s="40" t="s">
+        <v>117</v>
+      </c>
+      <c r="J6" s="24" t="s">
         <v>109</v>
       </c>
-      <c r="G6" s="26">
-        <v>3214533321</v>
-      </c>
-      <c r="H6" s="27" t="s">
-        <v>119</v>
-      </c>
-      <c r="I6" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="J6" s="26" t="s">
-        <v>112</v>
-      </c>
-      <c r="K6" s="26" t="str">
+      <c r="K6" s="24" t="str">
         <f>_xlfn.CONCAT(B6,"-",C6,"-",D6,"-",E6,"-",F6,"-",G6)</f>
         <v>Carlos--Arbeladez--+57-3214533321</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7" s="26">
+      <c r="A7" s="24">
         <v>4</v>
       </c>
-      <c r="B7" s="26" t="s">
+      <c r="B7" s="24" t="s">
+        <v>118</v>
+      </c>
+      <c r="C7" s="24"/>
+      <c r="D7" s="24" t="s">
+        <v>119</v>
+      </c>
+      <c r="E7" s="24" t="s">
+        <v>120</v>
+      </c>
+      <c r="F7" s="38" t="s">
         <v>121</v>
       </c>
-      <c r="C7" s="26"/>
-      <c r="D7" s="26" t="s">
+      <c r="G7" s="24">
+        <v>9876543210</v>
+      </c>
+      <c r="H7" s="25" t="s">
         <v>122</v>
       </c>
-      <c r="E7" s="26" t="s">
+      <c r="I7" s="39" t="s">
         <v>123</v>
       </c>
-      <c r="F7" s="40" t="s">
+      <c r="J7" s="24" t="s">
         <v>124</v>
       </c>
-      <c r="G7" s="26">
-        <v>9876543210</v>
-      </c>
-      <c r="H7" s="27" t="s">
-        <v>125</v>
-      </c>
-      <c r="I7" s="41" t="s">
-        <v>126</v>
-      </c>
-      <c r="J7" s="26" t="s">
-        <v>127</v>
-      </c>
-      <c r="K7" s="26" t="str">
+      <c r="K7" s="24" t="str">
         <f>_xlfn.CONCAT(B7,"-",C7,"-",D7,"-",E7,"-",F7,"-",G7)</f>
         <v>Andres--Ramirez-Patiño-+91-9876543210</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A8" s="26">
+      <c r="A8" s="24">
         <v>5</v>
       </c>
-      <c r="B8" s="26" t="s">
-        <v>105</v>
-      </c>
-      <c r="C8" s="26" t="s">
+      <c r="B8" s="24" t="s">
+        <v>102</v>
+      </c>
+      <c r="C8" s="24" t="s">
         <v>76</v>
       </c>
-      <c r="D8" s="26" t="s">
+      <c r="D8" s="24" t="s">
+        <v>125</v>
+      </c>
+      <c r="E8" s="24" t="s">
+        <v>126</v>
+      </c>
+      <c r="F8" s="38" t="s">
+        <v>127</v>
+      </c>
+      <c r="G8" s="24">
+        <v>998765432</v>
+      </c>
+      <c r="H8" s="25" t="s">
         <v>128</v>
       </c>
-      <c r="E8" s="26" t="s">
+      <c r="I8" s="24" t="s">
         <v>129</v>
       </c>
-      <c r="F8" s="40" t="s">
-        <v>130</v>
-      </c>
-      <c r="G8" s="26">
-        <v>998765432</v>
-      </c>
-      <c r="H8" s="27" t="s">
-        <v>131</v>
-      </c>
-      <c r="I8" s="26" t="s">
-        <v>132</v>
-      </c>
-      <c r="J8" s="26" t="s">
-        <v>127</v>
-      </c>
-      <c r="K8" s="26" t="str">
+      <c r="J8" s="24" t="s">
+        <v>124</v>
+      </c>
+      <c r="K8" s="24" t="str">
         <f>_xlfn.CONCAT(B8,"-",C8,"-",D8,"-",E8,"-",F8,"-",G8)</f>
         <v>Juan-Carlos-Zambrano-Perez-+593-998765432</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="28"/>
-      <c r="B14" s="29" t="s">
+      <c r="A14" s="26"/>
+      <c r="B14" s="27" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="30"/>
-      <c r="B15" s="29" t="s">
+      <c r="A15" s="28"/>
+      <c r="B15" s="27" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="31"/>
-      <c r="B16" s="29" t="s">
+      <c r="A16" s="29"/>
+      <c r="B16" s="27" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="43"/>
-      <c r="B17" s="29" t="s">
-        <v>133</v>
+      <c r="A17" s="41"/>
+      <c r="B17" s="27" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="44"/>
-      <c r="B18" s="29" t="s">
-        <v>134</v>
+      <c r="A18" s="42"/>
+      <c r="B18" s="27" t="s">
+        <v>131</v>
       </c>
     </row>
   </sheetData>
@@ -15110,7 +15064,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:U19"/>
+  <dimension ref="A1:W19"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="27" customWidth="1"/>
@@ -15135,15 +15089,15 @@
     <col min="21" max="21" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A1" s="32" t="s">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A1" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="32" t="s">
+      <c r="B1" s="30" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
         <v>34</v>
       </c>
@@ -15208,7 +15162,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A3" s="13" t="str">
         <f>'M-Cliente'!A3</f>
         <v>id</v>
@@ -15235,7 +15189,7 @@
       <c r="L3" s="13"/>
       <c r="M3" s="14"/>
       <c r="N3" s="13" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="O3" s="13" t="s">
         <v>57</v>
@@ -15255,7 +15209,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="4" spans="1:21" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A4" s="13" t="str">
         <f>'M-Cliente'!B3</f>
         <v>primerNombre</v>
@@ -15268,7 +15222,7 @@
         <v>57</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="E4" s="13" t="s">
         <v>55</v>
@@ -15306,7 +15260,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="5" spans="1:21" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A5" s="13" t="str">
         <f>'M-Cliente'!C3</f>
         <v>segundoNombre</v>
@@ -15319,7 +15273,7 @@
         <v>57</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="E5" s="13" t="s">
         <v>57</v>
@@ -15357,7 +15311,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="6" spans="1:21" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A6" s="13" t="str">
         <f>'M-Cliente'!D3</f>
         <v>primerApellido</v>
@@ -15370,7 +15324,7 @@
         <v>57</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="E6" s="13" t="s">
         <v>55</v>
@@ -15408,7 +15362,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="7" spans="1:21" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A7" s="13" t="str">
         <f>'M-Cliente'!E3</f>
         <v>segundoApellido</v>
@@ -15421,7 +15375,7 @@
         <v>57</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="E7" s="13" t="s">
         <v>57</v>
@@ -15459,7 +15413,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="8" spans="1:21" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A8" s="13" t="str">
         <f>'M-Cliente'!F3</f>
         <v>prefijoCelular</v>
@@ -15507,12 +15461,14 @@
       <c r="S8" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="T8" s="13"/>
+      <c r="T8" s="135" t="s">
+        <v>328</v>
+      </c>
       <c r="U8" s="13" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="9" spans="1:21" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A9" s="13" t="str">
         <f>'M-Cliente'!G3</f>
         <v>celular</v>
@@ -15525,25 +15481,25 @@
         <v>57</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>82</v>
+        <v>58</v>
       </c>
       <c r="E9" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="F9" s="13"/>
-      <c r="G9" s="13"/>
+      <c r="F9" s="13">
+        <v>4</v>
+      </c>
+      <c r="G9" s="13">
+        <v>15</v>
+      </c>
       <c r="H9" s="13"/>
       <c r="I9" s="13"/>
-      <c r="J9" s="13">
-        <v>3000000000</v>
-      </c>
-      <c r="K9" s="13">
-        <v>3999999999</v>
-      </c>
-      <c r="L9" s="13"/>
-      <c r="M9" s="14" t="s">
-        <v>83</v>
-      </c>
+      <c r="J9" s="13"/>
+      <c r="K9" s="13"/>
+      <c r="L9" s="14" t="s">
+        <v>329</v>
+      </c>
+      <c r="M9" s="14"/>
       <c r="N9" s="13" t="s">
         <v>57</v>
       </c>
@@ -15552,10 +15508,10 @@
       </c>
       <c r="P9" s="13"/>
       <c r="Q9" s="13" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="R9" s="13" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="S9" s="13" t="s">
         <v>57</v>
@@ -15565,7 +15521,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="10" spans="1:21" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A10" s="13" t="str">
         <f>'M-Cliente'!H3</f>
         <v>multasSinPagar</v>
@@ -15578,7 +15534,7 @@
         <v>57</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>82</v>
+        <v>332</v>
       </c>
       <c r="E10" s="13" t="s">
         <v>55</v>
@@ -15587,13 +15543,11 @@
       <c r="G10" s="13"/>
       <c r="H10" s="13"/>
       <c r="I10" s="13"/>
-      <c r="J10" s="13">
-        <v>0</v>
-      </c>
+      <c r="J10" s="13"/>
       <c r="K10" s="13"/>
       <c r="L10" s="13"/>
       <c r="M10" s="14" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="N10" s="13" t="s">
         <v>55</v>
@@ -15602,21 +15556,17 @@
         <v>57</v>
       </c>
       <c r="P10" s="13"/>
-      <c r="Q10" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="R10" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="S10" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="T10" s="13"/>
+      <c r="Q10" s="13"/>
+      <c r="R10" s="13"/>
+      <c r="S10" s="13"/>
+      <c r="T10" s="13">
+        <v>0</v>
+      </c>
       <c r="U10" s="13" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="11" spans="1:21" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:23" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A11" s="13" t="str">
         <f>'M-Cliente'!I3</f>
         <v>estaVetado</v>
@@ -15629,7 +15579,7 @@
         <v>57</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E11" s="13" t="s">
         <v>55</v>
@@ -15642,7 +15592,7 @@
       <c r="K11" s="13"/>
       <c r="L11" s="13"/>
       <c r="M11" s="14" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="N11" s="13" t="s">
         <v>55</v>
@@ -15651,21 +15601,17 @@
         <v>57</v>
       </c>
       <c r="P11" s="13"/>
-      <c r="Q11" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="R11" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="S11" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="T11" s="13"/>
+      <c r="Q11" s="13"/>
+      <c r="R11" s="13"/>
+      <c r="S11" s="13"/>
+      <c r="T11" s="13" t="s">
+        <v>57</v>
+      </c>
       <c r="U11" s="13" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A12" s="4"/>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
@@ -15688,7 +15634,7 @@
       <c r="T12" s="4"/>
       <c r="U12" s="4"/>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A13" s="17" t="s">
         <v>61</v>
       </c>
@@ -15698,35 +15644,37 @@
       <c r="C13" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="D13" s="33"/>
-      <c r="E13" s="33"/>
-      <c r="F13" s="33"/>
-      <c r="G13" s="33"/>
-      <c r="H13" s="33"/>
-      <c r="I13" s="33"/>
-      <c r="J13" s="33"/>
-      <c r="K13" s="33"/>
-      <c r="L13" s="33"/>
-      <c r="M13" s="33"/>
-      <c r="N13" s="33"/>
-      <c r="O13" s="33"/>
-      <c r="P13" s="33"/>
-      <c r="Q13" s="33"/>
-      <c r="R13" s="33"/>
-      <c r="S13" s="33"/>
-      <c r="T13" s="33"/>
-      <c r="U13" s="33"/>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A14" s="134" t="str">
+      <c r="D13" s="136"/>
+      <c r="E13" s="136"/>
+      <c r="F13" s="136"/>
+      <c r="G13" s="136"/>
+      <c r="H13" s="136"/>
+      <c r="I13" s="136"/>
+      <c r="J13" s="136"/>
+      <c r="K13" s="136"/>
+      <c r="L13" s="136"/>
+      <c r="M13" s="136"/>
+      <c r="N13" s="136"/>
+      <c r="O13" s="136"/>
+      <c r="P13" s="136"/>
+      <c r="Q13" s="136"/>
+      <c r="R13" s="136"/>
+      <c r="S13" s="136"/>
+      <c r="T13" s="136"/>
+      <c r="U13" s="136"/>
+      <c r="V13" s="137"/>
+      <c r="W13" s="137"/>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A14" s="131" t="str">
         <f>'M-Cliente'!J3</f>
         <v>Combinación única</v>
       </c>
-      <c r="B14" s="135" t="str">
+      <c r="B14" s="132" t="str">
         <f>'M-Cliente'!J2</f>
         <v>Combinacion única que indica que no puede existir más de un cliente con un mismo nombre, apellidos, prefijo de celular y número de celular</v>
       </c>
-      <c r="C14" s="34" t="str">
+      <c r="C14" s="32" t="str">
         <f t="shared" ref="C14:C19" si="0">A4</f>
         <v>primerNombre</v>
       </c>
@@ -15749,10 +15697,10 @@
       <c r="T14" s="4"/>
       <c r="U14" s="4"/>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A15" s="134"/>
-      <c r="B15" s="134"/>
-      <c r="C15" s="34" t="str">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A15" s="131"/>
+      <c r="B15" s="131"/>
+      <c r="C15" s="32" t="str">
         <f t="shared" si="0"/>
         <v>segundoNombre</v>
       </c>
@@ -15775,10 +15723,10 @@
       <c r="T15" s="4"/>
       <c r="U15" s="4"/>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A16" s="134"/>
-      <c r="B16" s="134"/>
-      <c r="C16" s="34" t="str">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A16" s="131"/>
+      <c r="B16" s="131"/>
+      <c r="C16" s="32" t="str">
         <f t="shared" si="0"/>
         <v>primerApellido</v>
       </c>
@@ -15802,9 +15750,9 @@
       <c r="U16" s="4"/>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A17" s="134"/>
-      <c r="B17" s="134"/>
-      <c r="C17" s="34" t="str">
+      <c r="A17" s="131"/>
+      <c r="B17" s="131"/>
+      <c r="C17" s="32" t="str">
         <f t="shared" si="0"/>
         <v>segundoApellido</v>
       </c>
@@ -15828,9 +15776,9 @@
       <c r="U17" s="4"/>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A18" s="134"/>
-      <c r="B18" s="134"/>
-      <c r="C18" s="34" t="str">
+      <c r="A18" s="131"/>
+      <c r="B18" s="131"/>
+      <c r="C18" s="32" t="str">
         <f t="shared" si="0"/>
         <v>prefijoCelular</v>
       </c>
@@ -15854,9 +15802,9 @@
       <c r="U18" s="4"/>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A19" s="134"/>
-      <c r="B19" s="134"/>
-      <c r="C19" s="34" t="str">
+      <c r="A19" s="131"/>
+      <c r="B19" s="131"/>
+      <c r="C19" s="32" t="str">
         <f t="shared" si="0"/>
         <v>celular</v>
       </c>
